--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\land\PLANAbPiaSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\land\PLANAbPiaSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD6CD2D-AE1B-423B-9A95-7F3C436C29B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891FB75-0F32-495E-81CB-E9AA727372B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId10"/>
+    <pivotCache cacheId="12" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -8245,7 +8245,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F9A18EA-B1D4-4240-B553-42848006A3CE}" name="PivotTable2" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F9A18EA-B1D4-4240-B553-42848006A3CE}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:F16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -8668,18 +8668,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="75.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="75.26953125" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -8687,130 +8687,130 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="5">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" s="4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" s="5" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" s="8" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" s="9"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B16" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B17" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B18" s="5">
         <v>2016</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B19" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B20" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B21" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B23" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>355</v>
       </c>
@@ -8829,14 +8829,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34DB6CD0-7C30-4BD3-9788-250A76B3BC98}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K602"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="4" width="11.42578125" style="59"/>
-    <col min="5" max="5" width="18.28515625" style="59" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="59"/>
+    <col min="1" max="4" width="11.40625" style="59"/>
+    <col min="5" max="5" width="18.26953125" style="59" customWidth="1"/>
+    <col min="6" max="16384" width="11.40625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="67" t="s">
         <v>285</v>
       </c>
@@ -8849,7 +8849,7 @@
       <c r="H1" s="67"/>
       <c r="I1" s="67"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A2" s="59" t="s">
         <v>286</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A3" s="59" t="s">
         <v>295</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A4" s="59" t="s">
         <v>295</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A5" s="59" t="s">
         <v>295</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A6" s="59" t="s">
         <v>295</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A7" s="59" t="s">
         <v>295</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A8" s="59" t="s">
         <v>295</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A9" s="59" t="s">
         <v>295</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A10" s="59" t="s">
         <v>295</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A11" s="59" t="s">
         <v>295</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A12" s="59" t="s">
         <v>295</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A13" s="59" t="s">
         <v>295</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A14" s="59" t="s">
         <v>295</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A15" s="59" t="s">
         <v>295</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A16" s="59" t="s">
         <v>295</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A17" s="59" t="s">
         <v>295</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A18" s="59" t="s">
         <v>295</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A19" s="59" t="s">
         <v>295</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A20" s="59" t="s">
         <v>295</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A21" s="59" t="s">
         <v>295</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A22" s="59" t="s">
         <v>295</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A23" s="59" t="s">
         <v>295</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A24" s="59" t="s">
         <v>295</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A25" s="59" t="s">
         <v>295</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A26" s="59" t="s">
         <v>295</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A27" s="59" t="s">
         <v>295</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A28" s="59" t="s">
         <v>295</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A29" s="59" t="s">
         <v>295</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A30" s="59" t="s">
         <v>295</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A31" s="59" t="s">
         <v>295</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A32" s="59" t="s">
         <v>295</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A33" s="59" t="s">
         <v>295</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A34" s="59" t="s">
         <v>295</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A35" s="59" t="s">
         <v>295</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A36" s="59" t="s">
         <v>295</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A37" s="59" t="s">
         <v>295</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A38" s="59" t="s">
         <v>295</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A39" s="59" t="s">
         <v>295</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A40" s="59" t="s">
         <v>295</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A41" s="59" t="s">
         <v>295</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A42" s="59" t="s">
         <v>295</v>
       </c>
@@ -10137,7 +10137,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A43" s="59" t="s">
         <v>295</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A44" s="59" t="s">
         <v>295</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A45" s="59" t="s">
         <v>295</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A46" s="59" t="s">
         <v>295</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A47" s="59" t="s">
         <v>295</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A48" s="59" t="s">
         <v>295</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A49" s="59" t="s">
         <v>295</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A50" s="59" t="s">
         <v>295</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A51" s="59" t="s">
         <v>295</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A52" s="59" t="s">
         <v>295</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A53" s="59" t="s">
         <v>295</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A54" s="59" t="s">
         <v>295</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A55" s="59" t="s">
         <v>295</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A56" s="59" t="s">
         <v>295</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A57" s="59" t="s">
         <v>295</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A58" s="59" t="s">
         <v>295</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A59" s="59" t="s">
         <v>295</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A60" s="59" t="s">
         <v>295</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A61" s="59" t="s">
         <v>295</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A62" s="59" t="s">
         <v>295</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A63" s="59" t="s">
         <v>295</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A64" s="59" t="s">
         <v>295</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A65" s="59" t="s">
         <v>295</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A66" s="59" t="s">
         <v>295</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A67" s="59" t="s">
         <v>295</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A68" s="59" t="s">
         <v>295</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A69" s="59" t="s">
         <v>295</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A70" s="59" t="s">
         <v>295</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A71" s="59" t="s">
         <v>295</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A72" s="59" t="s">
         <v>295</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A73" s="59" t="s">
         <v>295</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A74" s="59" t="s">
         <v>295</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A75" s="59" t="s">
         <v>295</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A76" s="59" t="s">
         <v>295</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A77" s="59" t="s">
         <v>295</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A78" s="59" t="s">
         <v>295</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A79" s="59" t="s">
         <v>295</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A80" s="59" t="s">
         <v>295</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A81" s="59" t="s">
         <v>295</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A82" s="59" t="s">
         <v>295</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A83" s="59" t="s">
         <v>295</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A84" s="59" t="s">
         <v>295</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A85" s="59" t="s">
         <v>295</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A86" s="59" t="s">
         <v>295</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A87" s="59" t="s">
         <v>295</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A88" s="59" t="s">
         <v>295</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A89" s="59" t="s">
         <v>295</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A90" s="59" t="s">
         <v>295</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A91" s="59" t="s">
         <v>295</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A92" s="59" t="s">
         <v>295</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A93" s="59" t="s">
         <v>295</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A94" s="59" t="s">
         <v>295</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A95" s="59" t="s">
         <v>295</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A96" s="59" t="s">
         <v>295</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A97" s="59" t="s">
         <v>295</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A98" s="59" t="s">
         <v>295</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A99" s="59" t="s">
         <v>295</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A100" s="59" t="s">
         <v>295</v>
       </c>
@@ -11926,7 +11926,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A101" s="59" t="s">
         <v>295</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A102" s="59" t="s">
         <v>295</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A103" s="59" t="s">
         <v>295</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A104" s="59" t="s">
         <v>295</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A105" s="59" t="s">
         <v>295</v>
       </c>
@@ -12071,7 +12071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A106" s="59" t="s">
         <v>295</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A107" s="59" t="s">
         <v>295</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A108" s="59" t="s">
         <v>295</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A109" s="59" t="s">
         <v>295</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A110" s="59" t="s">
         <v>295</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A111" s="59" t="s">
         <v>295</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A112" s="59" t="s">
         <v>295</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A113" s="59" t="s">
         <v>295</v>
       </c>
@@ -12303,7 +12303,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A114" s="59" t="s">
         <v>295</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A115" s="59" t="s">
         <v>295</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A116" s="59" t="s">
         <v>295</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A117" s="59" t="s">
         <v>295</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A118" s="59" t="s">
         <v>295</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A119" s="59" t="s">
         <v>295</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A120" s="59" t="s">
         <v>295</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A121" s="59" t="s">
         <v>295</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A122" s="59" t="s">
         <v>295</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A123" s="59" t="s">
         <v>295</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A124" s="59" t="s">
         <v>295</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A125" s="59" t="s">
         <v>295</v>
       </c>
@@ -12651,7 +12651,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A126" s="59" t="s">
         <v>295</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A127" s="59" t="s">
         <v>295</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A128" s="59" t="s">
         <v>295</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A129" s="59" t="s">
         <v>295</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A130" s="59" t="s">
         <v>295</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A131" s="59" t="s">
         <v>295</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A132" s="59" t="s">
         <v>295</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A133" s="59" t="s">
         <v>295</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A134" s="59" t="s">
         <v>295</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A135" s="59" t="s">
         <v>295</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A136" s="59" t="s">
         <v>295</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A137" s="59" t="s">
         <v>295</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A138" s="59" t="s">
         <v>295</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A139" s="59" t="s">
         <v>295</v>
       </c>
@@ -13057,7 +13057,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A140" s="59" t="s">
         <v>295</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A141" s="59" t="s">
         <v>295</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A142" s="59" t="s">
         <v>295</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A143" s="59" t="s">
         <v>295</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A144" s="59" t="s">
         <v>295</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A145" s="59" t="s">
         <v>295</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A146" s="59" t="s">
         <v>295</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A147" s="59" t="s">
         <v>295</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A148" s="59" t="s">
         <v>295</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A149" s="59" t="s">
         <v>295</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A150" s="59" t="s">
         <v>295</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A151" s="59" t="s">
         <v>295</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A152" s="59" t="s">
         <v>295</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A153" s="59" t="s">
         <v>295</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A154" s="59" t="s">
         <v>295</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A155" s="59" t="s">
         <v>295</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A156" s="59" t="s">
         <v>295</v>
       </c>
@@ -13558,7 +13558,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A157" s="59" t="s">
         <v>295</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A158" s="59" t="s">
         <v>295</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A159" s="59" t="s">
         <v>295</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A160" s="59" t="s">
         <v>295</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A161" s="59" t="s">
         <v>295</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A162" s="59" t="s">
         <v>295</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A163" s="59" t="s">
         <v>295</v>
       </c>
@@ -13781,7 +13781,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A164" s="59" t="s">
         <v>295</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A165" s="59" t="s">
         <v>295</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A166" s="59" t="s">
         <v>295</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A167" s="59" t="s">
         <v>295</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A168" s="59" t="s">
         <v>295</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A169" s="59" t="s">
         <v>295</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A170" s="59" t="s">
         <v>295</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A171" s="59" t="s">
         <v>295</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A172" s="59" t="s">
         <v>295</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A173" s="59" t="s">
         <v>295</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A174" s="59" t="s">
         <v>295</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A175" s="59" t="s">
         <v>295</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A176" s="59" t="s">
         <v>295</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A177" s="59" t="s">
         <v>295</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A178" s="59" t="s">
         <v>295</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A179" s="59" t="s">
         <v>295</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A180" s="59" t="s">
         <v>295</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A181" s="59" t="s">
         <v>295</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A182" s="59" t="s">
         <v>295</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A183" s="59" t="s">
         <v>295</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A184" s="59" t="s">
         <v>295</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A185" s="59" t="s">
         <v>295</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A186" s="59" t="s">
         <v>295</v>
       </c>
@@ -14500,7 +14500,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A187" s="59" t="s">
         <v>295</v>
       </c>
@@ -14529,7 +14529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A188" s="59" t="s">
         <v>295</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A189" s="59" t="s">
         <v>295</v>
       </c>
@@ -14591,7 +14591,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A190" s="59" t="s">
         <v>295</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A191" s="59" t="s">
         <v>295</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A192" s="59" t="s">
         <v>295</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A193" s="59" t="s">
         <v>295</v>
       </c>
@@ -14723,7 +14723,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A194" s="59" t="s">
         <v>295</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A195" s="59" t="s">
         <v>295</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A196" s="59" t="s">
         <v>295</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A197" s="59" t="s">
         <v>295</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A198" s="59" t="s">
         <v>295</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A199" s="59" t="s">
         <v>295</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A200" s="59" t="s">
         <v>295</v>
       </c>
@@ -14932,7 +14932,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A201" s="59" t="s">
         <v>295</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A202" s="59" t="s">
         <v>295</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A203" s="59" t="s">
         <v>295</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A204" s="59" t="s">
         <v>295</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A205" s="59" t="s">
         <v>295</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A206" s="59" t="s">
         <v>295</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A207" s="59" t="s">
         <v>295</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A208" s="59" t="s">
         <v>295</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A209" s="59" t="s">
         <v>295</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A210" s="59" t="s">
         <v>295</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A211" s="59" t="s">
         <v>295</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A212" s="59" t="s">
         <v>295</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A213" s="59" t="s">
         <v>295</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A214" s="59" t="s">
         <v>295</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A215" s="59" t="s">
         <v>295</v>
       </c>
@@ -15407,7 +15407,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A216" s="59" t="s">
         <v>295</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A217" s="59" t="s">
         <v>295</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A218" s="59" t="s">
         <v>295</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A219" s="59" t="s">
         <v>295</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A220" s="59" t="s">
         <v>295</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A221" s="59" t="s">
         <v>295</v>
       </c>
@@ -15593,7 +15593,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A222" s="59" t="s">
         <v>295</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A223" s="59" t="s">
         <v>295</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A224" s="59" t="s">
         <v>295</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A225" s="59" t="s">
         <v>295</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A226" s="59" t="s">
         <v>295</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A227" s="59" t="s">
         <v>295</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A228" s="59" t="s">
         <v>295</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A229" s="59" t="s">
         <v>295</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A230" s="59" t="s">
         <v>295</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A231" s="59" t="s">
         <v>295</v>
       </c>
@@ -15907,7 +15907,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A232" s="59" t="s">
         <v>295</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A233" s="59" t="s">
         <v>295</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A234" s="59" t="s">
         <v>295</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A235" s="59" t="s">
         <v>295</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A236" s="59" t="s">
         <v>295</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A237" s="59" t="s">
         <v>295</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A238" s="59" t="s">
         <v>295</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A239" s="59" t="s">
         <v>295</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A240" s="59" t="s">
         <v>295</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A241" s="59" t="s">
         <v>295</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A242" s="59" t="s">
         <v>295</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A243" s="59" t="s">
         <v>295</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A244" s="59" t="s">
         <v>295</v>
       </c>
@@ -16308,7 +16308,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A245" s="59" t="s">
         <v>295</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A246" s="59" t="s">
         <v>295</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A247" s="59" t="s">
         <v>295</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A248" s="59" t="s">
         <v>295</v>
       </c>
@@ -16424,7 +16424,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A249" s="59" t="s">
         <v>295</v>
       </c>
@@ -16453,7 +16453,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A250" s="59" t="s">
         <v>295</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A251" s="59" t="s">
         <v>295</v>
       </c>
@@ -16511,7 +16511,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A252" s="59" t="s">
         <v>295</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A253" s="59" t="s">
         <v>295</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A254" s="59" t="s">
         <v>295</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A255" s="59" t="s">
         <v>295</v>
       </c>
@@ -16627,7 +16627,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A256" s="59" t="s">
         <v>295</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A257" s="59" t="s">
         <v>295</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A258" s="59" t="s">
         <v>295</v>
       </c>
@@ -16714,7 +16714,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A259" s="59" t="s">
         <v>295</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A260" s="59" t="s">
         <v>295</v>
       </c>
@@ -16772,7 +16772,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A261" s="59" t="s">
         <v>295</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A262" s="59" t="s">
         <v>295</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A263" s="59" t="s">
         <v>295</v>
       </c>
@@ -16859,7 +16859,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A264" s="59" t="s">
         <v>295</v>
       </c>
@@ -16888,7 +16888,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A265" s="59" t="s">
         <v>295</v>
       </c>
@@ -16917,7 +16917,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A266" s="59" t="s">
         <v>295</v>
       </c>
@@ -16946,7 +16946,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A267" s="59" t="s">
         <v>295</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A268" s="59" t="s">
         <v>295</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A269" s="59" t="s">
         <v>295</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A270" s="59" t="s">
         <v>295</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A271" s="59" t="s">
         <v>295</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A272" s="59" t="s">
         <v>295</v>
       </c>
@@ -17120,7 +17120,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A273" s="59" t="s">
         <v>295</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A274" s="59" t="s">
         <v>295</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A275" s="59" t="s">
         <v>295</v>
       </c>
@@ -17207,7 +17207,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A276" s="59" t="s">
         <v>295</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A277" s="59" t="s">
         <v>295</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A278" s="59" t="s">
         <v>295</v>
       </c>
@@ -17294,7 +17294,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A279" s="59" t="s">
         <v>295</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A280" s="59" t="s">
         <v>295</v>
       </c>
@@ -17352,7 +17352,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A281" s="59" t="s">
         <v>295</v>
       </c>
@@ -17381,7 +17381,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A282" s="59" t="s">
         <v>295</v>
       </c>
@@ -17410,7 +17410,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A283" s="59" t="s">
         <v>295</v>
       </c>
@@ -17439,7 +17439,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A284" s="59" t="s">
         <v>295</v>
       </c>
@@ -17468,7 +17468,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A285" s="59" t="s">
         <v>295</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A286" s="59" t="s">
         <v>295</v>
       </c>
@@ -17526,7 +17526,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A287" s="59" t="s">
         <v>295</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A288" s="59" t="s">
         <v>295</v>
       </c>
@@ -17584,7 +17584,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A289" s="59" t="s">
         <v>295</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A290" s="59" t="s">
         <v>295</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A291" s="59" t="s">
         <v>295</v>
       </c>
@@ -17671,7 +17671,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A292" s="59" t="s">
         <v>295</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A293" s="59" t="s">
         <v>295</v>
       </c>
@@ -17729,7 +17729,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A294" s="59" t="s">
         <v>295</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A295" s="59" t="s">
         <v>295</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A296" s="59" t="s">
         <v>295</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A297" s="59" t="s">
         <v>295</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A298" s="59" t="s">
         <v>295</v>
       </c>
@@ -17874,7 +17874,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A299" s="59" t="s">
         <v>295</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A300" s="59" t="s">
         <v>295</v>
       </c>
@@ -17932,7 +17932,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A301" s="59" t="s">
         <v>295</v>
       </c>
@@ -17961,7 +17961,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A302" s="59" t="s">
         <v>295</v>
       </c>
@@ -17990,7 +17990,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A303" s="59" t="s">
         <v>295</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A304" s="59" t="s">
         <v>295</v>
       </c>
@@ -18048,7 +18048,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A305" s="59" t="s">
         <v>295</v>
       </c>
@@ -18077,7 +18077,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A306" s="59" t="s">
         <v>295</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A307" s="59" t="s">
         <v>295</v>
       </c>
@@ -18139,7 +18139,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A308" s="59" t="s">
         <v>295</v>
       </c>
@@ -18172,7 +18172,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A309" s="59" t="s">
         <v>295</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A310" s="59" t="s">
         <v>295</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A311" s="59" t="s">
         <v>295</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A312" s="59" t="s">
         <v>295</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A313" s="59" t="s">
         <v>295</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A314" s="59" t="s">
         <v>295</v>
       </c>
@@ -18354,7 +18354,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A315" s="59" t="s">
         <v>295</v>
       </c>
@@ -18383,7 +18383,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A316" s="59" t="s">
         <v>295</v>
       </c>
@@ -18412,7 +18412,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A317" s="59" t="s">
         <v>295</v>
       </c>
@@ -18445,7 +18445,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A318" s="59" t="s">
         <v>295</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A319" s="59" t="s">
         <v>295</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A320" s="59" t="s">
         <v>295</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A321" s="59" t="s">
         <v>295</v>
       </c>
@@ -18573,7 +18573,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A322" s="59" t="s">
         <v>295</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A323" s="59" t="s">
         <v>295</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A324" s="59" t="s">
         <v>295</v>
       </c>
@@ -18660,7 +18660,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A325" s="59" t="s">
         <v>295</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A326" s="59" t="s">
         <v>295</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A327" s="59" t="s">
         <v>295</v>
       </c>
@@ -18751,7 +18751,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A328" s="59" t="s">
         <v>295</v>
       </c>
@@ -18784,7 +18784,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A329" s="59" t="s">
         <v>295</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A330" s="59" t="s">
         <v>295</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A331" s="59" t="s">
         <v>295</v>
       </c>
@@ -18879,7 +18879,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A332" s="59" t="s">
         <v>295</v>
       </c>
@@ -18908,7 +18908,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A333" s="59" t="s">
         <v>295</v>
       </c>
@@ -18937,7 +18937,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A334" s="59" t="s">
         <v>295</v>
       </c>
@@ -18966,7 +18966,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A335" s="59" t="s">
         <v>295</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A336" s="59" t="s">
         <v>295</v>
       </c>
@@ -19024,7 +19024,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A337" s="59" t="s">
         <v>295</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A338" s="59" t="s">
         <v>295</v>
       </c>
@@ -19090,7 +19090,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A339" s="59" t="s">
         <v>295</v>
       </c>
@@ -19123,7 +19123,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A340" s="59" t="s">
         <v>295</v>
       </c>
@@ -19156,7 +19156,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A341" s="59" t="s">
         <v>295</v>
       </c>
@@ -19185,7 +19185,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A342" s="59" t="s">
         <v>295</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A343" s="59" t="s">
         <v>295</v>
       </c>
@@ -19240,7 +19240,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A344" s="59" t="s">
         <v>295</v>
       </c>
@@ -19269,7 +19269,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A345" s="59" t="s">
         <v>295</v>
       </c>
@@ -19298,7 +19298,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A346" s="59" t="s">
         <v>295</v>
       </c>
@@ -19327,7 +19327,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A347" s="59" t="s">
         <v>295</v>
       </c>
@@ -19357,7 +19357,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A348" s="59" t="s">
         <v>295</v>
       </c>
@@ -19390,7 +19390,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A349" s="59" t="s">
         <v>295</v>
       </c>
@@ -19423,7 +19423,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A350" s="59" t="s">
         <v>295</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A351" s="59" t="s">
         <v>295</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A352" s="59" t="s">
         <v>295</v>
       </c>
@@ -19511,7 +19511,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A353" s="59" t="s">
         <v>295</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A354" s="59" t="s">
         <v>295</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A355" s="59" t="s">
         <v>295</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A356" s="59" t="s">
         <v>295</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A357" s="59" t="s">
         <v>295</v>
       </c>
@@ -19660,7 +19660,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A358" s="59" t="s">
         <v>295</v>
       </c>
@@ -19693,7 +19693,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A359" s="59" t="s">
         <v>295</v>
       </c>
@@ -19726,7 +19726,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A360" s="59" t="s">
         <v>295</v>
       </c>
@@ -19759,7 +19759,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A361" s="59" t="s">
         <v>295</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A362" s="59" t="s">
         <v>295</v>
       </c>
@@ -19817,7 +19817,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A363" s="59" t="s">
         <v>295</v>
       </c>
@@ -19846,7 +19846,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A364" s="59" t="s">
         <v>295</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A365" s="59" t="s">
         <v>295</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A366" s="59" t="s">
         <v>295</v>
       </c>
@@ -19933,7 +19933,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A367" s="59" t="s">
         <v>295</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A368" s="59" t="s">
         <v>295</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A369" s="59" t="s">
         <v>295</v>
       </c>
@@ -20032,7 +20032,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A370" s="59" t="s">
         <v>295</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A371" s="59" t="s">
         <v>295</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A372" s="59" t="s">
         <v>295</v>
       </c>
@@ -20123,7 +20123,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A373" s="59" t="s">
         <v>295</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A374" s="59" t="s">
         <v>295</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A375" s="59" t="s">
         <v>295</v>
       </c>
@@ -20210,7 +20210,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A376" s="59" t="s">
         <v>295</v>
       </c>
@@ -20239,7 +20239,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A377" s="59" t="s">
         <v>295</v>
       </c>
@@ -20272,7 +20272,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A378" s="59" t="s">
         <v>295</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A379" s="59" t="s">
         <v>295</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A380" s="59" t="s">
         <v>295</v>
       </c>
@@ -20371,7 +20371,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A381" s="59" t="s">
         <v>295</v>
       </c>
@@ -20400,7 +20400,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A382" s="59" t="s">
         <v>295</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A383" s="59" t="s">
         <v>295</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A384" s="59" t="s">
         <v>295</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A385" s="59" t="s">
         <v>295</v>
       </c>
@@ -20516,7 +20516,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A386" s="59" t="s">
         <v>295</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A387" s="59" t="s">
         <v>295</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A388" s="59" t="s">
         <v>295</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A389" s="59" t="s">
         <v>295</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A390" s="59" t="s">
         <v>295</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A391" s="59" t="s">
         <v>295</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A392" s="59" t="s">
         <v>295</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A393" s="59" t="s">
         <v>295</v>
       </c>
@@ -20768,7 +20768,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A394" s="59" t="s">
         <v>295</v>
       </c>
@@ -20797,7 +20797,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A395" s="59" t="s">
         <v>295</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A396" s="59" t="s">
         <v>295</v>
       </c>
@@ -20855,7 +20855,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A397" s="59" t="s">
         <v>295</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A398" s="59" t="s">
         <v>295</v>
       </c>
@@ -20913,7 +20913,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A399" s="59" t="s">
         <v>295</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A400" s="59" t="s">
         <v>295</v>
       </c>
@@ -20971,7 +20971,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A401" s="59" t="s">
         <v>295</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A402" s="59" t="s">
         <v>295</v>
       </c>
@@ -21029,7 +21029,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A403" s="59" t="s">
         <v>295</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A404" s="59" t="s">
         <v>295</v>
       </c>
@@ -21087,7 +21087,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A405" s="59" t="s">
         <v>295</v>
       </c>
@@ -21116,7 +21116,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A406" s="59" t="s">
         <v>295</v>
       </c>
@@ -21145,7 +21145,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A407" s="59" t="s">
         <v>295</v>
       </c>
@@ -21174,7 +21174,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A408" s="59" t="s">
         <v>295</v>
       </c>
@@ -21203,7 +21203,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A409" s="59" t="s">
         <v>295</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A410" s="59" t="s">
         <v>295</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A411" s="59" t="s">
         <v>295</v>
       </c>
@@ -21290,7 +21290,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A412" s="59" t="s">
         <v>295</v>
       </c>
@@ -21319,7 +21319,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A413" s="59" t="s">
         <v>295</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A414" s="59" t="s">
         <v>295</v>
       </c>
@@ -21377,7 +21377,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A415" s="59" t="s">
         <v>295</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A416" s="59" t="s">
         <v>295</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A417" s="59" t="s">
         <v>295</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A418" s="59" t="s">
         <v>295</v>
       </c>
@@ -21493,7 +21493,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A419" s="59" t="s">
         <v>295</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A420" s="59" t="s">
         <v>295</v>
       </c>
@@ -21551,7 +21551,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A421" s="59" t="s">
         <v>295</v>
       </c>
@@ -21580,7 +21580,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A422" s="59" t="s">
         <v>295</v>
       </c>
@@ -21609,7 +21609,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A423" s="59" t="s">
         <v>295</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A424" s="59" t="s">
         <v>295</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A425" s="59" t="s">
         <v>295</v>
       </c>
@@ -21696,7 +21696,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A426" s="59" t="s">
         <v>295</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A427" s="59" t="s">
         <v>295</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A428" s="59" t="s">
         <v>295</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A429" s="59" t="s">
         <v>295</v>
       </c>
@@ -21812,7 +21812,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A430" s="59" t="s">
         <v>295</v>
       </c>
@@ -21841,7 +21841,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A431" s="59" t="s">
         <v>295</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A432" s="59" t="s">
         <v>295</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A433" s="59" t="s">
         <v>295</v>
       </c>
@@ -21928,7 +21928,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A434" s="59" t="s">
         <v>295</v>
       </c>
@@ -21957,7 +21957,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A435" s="59" t="s">
         <v>295</v>
       </c>
@@ -21986,7 +21986,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A436" s="59" t="s">
         <v>295</v>
       </c>
@@ -22015,7 +22015,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A437" s="59" t="s">
         <v>295</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A438" s="59" t="s">
         <v>295</v>
       </c>
@@ -22073,7 +22073,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A439" s="59" t="s">
         <v>295</v>
       </c>
@@ -22102,7 +22102,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A440" s="59" t="s">
         <v>295</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A441" s="59" t="s">
         <v>295</v>
       </c>
@@ -22160,7 +22160,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A442" s="59" t="s">
         <v>295</v>
       </c>
@@ -22189,7 +22189,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A443" s="59" t="s">
         <v>295</v>
       </c>
@@ -22218,7 +22218,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A444" s="59" t="s">
         <v>295</v>
       </c>
@@ -22247,7 +22247,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A445" s="59" t="s">
         <v>295</v>
       </c>
@@ -22276,7 +22276,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A446" s="59" t="s">
         <v>295</v>
       </c>
@@ -22305,7 +22305,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A447" s="59" t="s">
         <v>295</v>
       </c>
@@ -22334,7 +22334,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A448" s="59" t="s">
         <v>295</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A449" s="59" t="s">
         <v>295</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A450" s="59" t="s">
         <v>295</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A451" s="59" t="s">
         <v>295</v>
       </c>
@@ -22450,7 +22450,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A452" s="59" t="s">
         <v>295</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A453" s="59" t="s">
         <v>295</v>
       </c>
@@ -22508,7 +22508,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A454" s="59" t="s">
         <v>295</v>
       </c>
@@ -22537,7 +22537,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A455" s="59" t="s">
         <v>295</v>
       </c>
@@ -22570,7 +22570,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A456" s="59" t="s">
         <v>295</v>
       </c>
@@ -22603,7 +22603,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A457" s="59" t="s">
         <v>295</v>
       </c>
@@ -22636,7 +22636,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A458" s="59" t="s">
         <v>295</v>
       </c>
@@ -22669,7 +22669,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A459" s="59" t="s">
         <v>295</v>
       </c>
@@ -22698,7 +22698,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A460" s="59" t="s">
         <v>295</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A461" s="59" t="s">
         <v>295</v>
       </c>
@@ -22756,7 +22756,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A462" s="59" t="s">
         <v>295</v>
       </c>
@@ -22785,7 +22785,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A463" s="59" t="s">
         <v>295</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A464" s="59" t="s">
         <v>295</v>
       </c>
@@ -22843,7 +22843,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A465" s="59" t="s">
         <v>295</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A466" s="59" t="s">
         <v>295</v>
       </c>
@@ -22909,7 +22909,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A467" s="59" t="s">
         <v>295</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A468" s="59" t="s">
         <v>295</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A469" s="59" t="s">
         <v>295</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A470" s="59" t="s">
         <v>295</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A471" s="59" t="s">
         <v>295</v>
       </c>
@@ -23062,7 +23062,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A472" s="59" t="s">
         <v>295</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A473" s="59" t="s">
         <v>295</v>
       </c>
@@ -23120,7 +23120,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A474" s="59" t="s">
         <v>295</v>
       </c>
@@ -23149,7 +23149,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A475" s="59" t="s">
         <v>295</v>
       </c>
@@ -23182,7 +23182,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A476" s="59" t="s">
         <v>295</v>
       </c>
@@ -23215,7 +23215,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A477" s="59" t="s">
         <v>295</v>
       </c>
@@ -23248,7 +23248,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A478" s="59" t="s">
         <v>295</v>
       </c>
@@ -23281,7 +23281,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A479" s="59" t="s">
         <v>295</v>
       </c>
@@ -23310,7 +23310,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A480" s="59" t="s">
         <v>295</v>
       </c>
@@ -23339,7 +23339,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A481" s="59" t="s">
         <v>295</v>
       </c>
@@ -23368,7 +23368,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A482" s="59" t="s">
         <v>295</v>
       </c>
@@ -23397,7 +23397,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A483" s="59" t="s">
         <v>295</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A484" s="59" t="s">
         <v>295</v>
       </c>
@@ -23455,7 +23455,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A485" s="59" t="s">
         <v>295</v>
       </c>
@@ -23488,7 +23488,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A486" s="59" t="s">
         <v>295</v>
       </c>
@@ -23521,7 +23521,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A487" s="59" t="s">
         <v>295</v>
       </c>
@@ -23554,7 +23554,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A488" s="59" t="s">
         <v>295</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A489" s="59" t="s">
         <v>295</v>
       </c>
@@ -23616,7 +23616,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A490" s="59" t="s">
         <v>295</v>
       </c>
@@ -23645,7 +23645,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A491" s="59" t="s">
         <v>295</v>
       </c>
@@ -23674,7 +23674,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A492" s="59" t="s">
         <v>295</v>
       </c>
@@ -23703,7 +23703,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A493" s="59" t="s">
         <v>295</v>
       </c>
@@ -23732,7 +23732,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A494" s="59" t="s">
         <v>295</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A495" s="59" t="s">
         <v>295</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A496" s="59" t="s">
         <v>295</v>
       </c>
@@ -23824,7 +23824,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A497" s="59" t="s">
         <v>295</v>
       </c>
@@ -23857,7 +23857,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A498" s="59" t="s">
         <v>295</v>
       </c>
@@ -23890,7 +23890,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A499" s="59" t="s">
         <v>295</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A500" s="59" t="s">
         <v>295</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A501" s="59" t="s">
         <v>295</v>
       </c>
@@ -23974,7 +23974,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A502" s="59" t="s">
         <v>295</v>
       </c>
@@ -24003,7 +24003,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A503" s="59" t="s">
         <v>295</v>
       </c>
@@ -24032,7 +24032,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A504" s="59" t="s">
         <v>295</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A505" s="59" t="s">
         <v>295</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A506" s="59" t="s">
         <v>295</v>
       </c>
@@ -24127,7 +24127,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A507" s="59" t="s">
         <v>295</v>
       </c>
@@ -24160,7 +24160,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A508" s="59" t="s">
         <v>295</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A509" s="59" t="s">
         <v>295</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A510" s="59" t="s">
         <v>295</v>
       </c>
@@ -24251,7 +24251,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A511" s="59" t="s">
         <v>295</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A512" s="59" t="s">
         <v>295</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A513" s="59" t="s">
         <v>295</v>
       </c>
@@ -24338,7 +24338,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A514" s="59" t="s">
         <v>295</v>
       </c>
@@ -24367,7 +24367,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A515" s="59" t="s">
         <v>295</v>
       </c>
@@ -24400,7 +24400,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A516" s="59" t="s">
         <v>295</v>
       </c>
@@ -24433,7 +24433,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A517" s="59" t="s">
         <v>295</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A518" s="59" t="s">
         <v>295</v>
       </c>
@@ -24499,7 +24499,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A519" s="59" t="s">
         <v>295</v>
       </c>
@@ -24528,7 +24528,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A520" s="59" t="s">
         <v>295</v>
       </c>
@@ -24557,7 +24557,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A521" s="59" t="s">
         <v>295</v>
       </c>
@@ -24586,7 +24586,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A522" s="59" t="s">
         <v>295</v>
       </c>
@@ -24615,7 +24615,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A523" s="59" t="s">
         <v>295</v>
       </c>
@@ -24644,7 +24644,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A524" s="59" t="s">
         <v>295</v>
       </c>
@@ -24673,7 +24673,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A525" s="59" t="s">
         <v>295</v>
       </c>
@@ -24706,7 +24706,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A526" s="59" t="s">
         <v>295</v>
       </c>
@@ -24739,7 +24739,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A527" s="59" t="s">
         <v>295</v>
       </c>
@@ -24772,7 +24772,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A528" s="59" t="s">
         <v>295</v>
       </c>
@@ -24805,7 +24805,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A529" s="59" t="s">
         <v>295</v>
       </c>
@@ -24834,7 +24834,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A530" s="59" t="s">
         <v>295</v>
       </c>
@@ -24863,7 +24863,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A531" s="59" t="s">
         <v>295</v>
       </c>
@@ -24892,7 +24892,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A532" s="59" t="s">
         <v>295</v>
       </c>
@@ -24921,7 +24921,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A533" s="59" t="s">
         <v>295</v>
       </c>
@@ -24950,7 +24950,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A534" s="59" t="s">
         <v>295</v>
       </c>
@@ -24979,7 +24979,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A535" s="59" t="s">
         <v>295</v>
       </c>
@@ -25008,7 +25008,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A536" s="59" t="s">
         <v>295</v>
       </c>
@@ -25037,7 +25037,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A537" s="59" t="s">
         <v>295</v>
       </c>
@@ -25066,7 +25066,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A538" s="59" t="s">
         <v>295</v>
       </c>
@@ -25099,7 +25099,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A539" s="59" t="s">
         <v>295</v>
       </c>
@@ -25132,7 +25132,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A540" s="59" t="s">
         <v>295</v>
       </c>
@@ -25165,7 +25165,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A541" s="59" t="s">
         <v>295</v>
       </c>
@@ -25198,7 +25198,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A542" s="59" t="s">
         <v>295</v>
       </c>
@@ -25231,7 +25231,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A543" s="59" t="s">
         <v>295</v>
       </c>
@@ -25260,7 +25260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A544" s="59" t="s">
         <v>295</v>
       </c>
@@ -25289,7 +25289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A545" s="59" t="s">
         <v>295</v>
       </c>
@@ -25318,7 +25318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A546" s="59" t="s">
         <v>295</v>
       </c>
@@ -25347,7 +25347,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A547" s="59" t="s">
         <v>295</v>
       </c>
@@ -25376,7 +25376,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A548" s="59" t="s">
         <v>295</v>
       </c>
@@ -25405,7 +25405,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A549" s="59" t="s">
         <v>295</v>
       </c>
@@ -25434,7 +25434,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A550" s="59" t="s">
         <v>295</v>
       </c>
@@ -25463,7 +25463,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A551" s="59" t="s">
         <v>295</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A552" s="59" t="s">
         <v>295</v>
       </c>
@@ -25521,7 +25521,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A553" s="59" t="s">
         <v>295</v>
       </c>
@@ -25550,7 +25550,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A554" s="59" t="s">
         <v>295</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A555" s="59" t="s">
         <v>295</v>
       </c>
@@ -25608,7 +25608,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A556" s="59" t="s">
         <v>295</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A557" s="59" t="s">
         <v>295</v>
       </c>
@@ -25666,7 +25666,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A558" s="59" t="s">
         <v>295</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A559" s="59" t="s">
         <v>295</v>
       </c>
@@ -25724,7 +25724,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A560" s="59" t="s">
         <v>295</v>
       </c>
@@ -25753,7 +25753,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A561" s="59" t="s">
         <v>295</v>
       </c>
@@ -25782,7 +25782,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A562" s="59" t="s">
         <v>295</v>
       </c>
@@ -25811,7 +25811,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A563" s="59" t="s">
         <v>295</v>
       </c>
@@ -25840,7 +25840,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A564" s="59" t="s">
         <v>295</v>
       </c>
@@ -25869,7 +25869,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A565" s="59" t="s">
         <v>295</v>
       </c>
@@ -25898,7 +25898,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A566" s="59" t="s">
         <v>295</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A567" s="59" t="s">
         <v>295</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A568" s="59" t="s">
         <v>295</v>
       </c>
@@ -25985,7 +25985,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A569" s="59" t="s">
         <v>295</v>
       </c>
@@ -26014,7 +26014,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A570" s="59" t="s">
         <v>295</v>
       </c>
@@ -26043,7 +26043,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A571" s="59" t="s">
         <v>295</v>
       </c>
@@ -26072,7 +26072,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A572" s="59" t="s">
         <v>295</v>
       </c>
@@ -26101,7 +26101,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A573" s="59" t="s">
         <v>295</v>
       </c>
@@ -26130,7 +26130,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A574" s="59" t="s">
         <v>295</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A575" s="59" t="s">
         <v>295</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A576" s="59" t="s">
         <v>295</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A577" s="59" t="s">
         <v>295</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A578" s="59" t="s">
         <v>295</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A579" s="59" t="s">
         <v>295</v>
       </c>
@@ -26304,7 +26304,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A580" s="59" t="s">
         <v>295</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A581" s="59" t="s">
         <v>295</v>
       </c>
@@ -26362,7 +26362,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A582" s="59" t="s">
         <v>295</v>
       </c>
@@ -26391,7 +26391,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A583" s="59" t="s">
         <v>295</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A584" s="59" t="s">
         <v>295</v>
       </c>
@@ -26449,7 +26449,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A585" s="59" t="s">
         <v>295</v>
       </c>
@@ -26478,7 +26478,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A586" s="59" t="s">
         <v>295</v>
       </c>
@@ -26507,7 +26507,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A587" s="59" t="s">
         <v>295</v>
       </c>
@@ -26536,7 +26536,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A588" s="59" t="s">
         <v>295</v>
       </c>
@@ -26565,7 +26565,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A589" s="59" t="s">
         <v>295</v>
       </c>
@@ -26594,7 +26594,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A590" s="59" t="s">
         <v>295</v>
       </c>
@@ -26623,7 +26623,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A591" s="59" t="s">
         <v>295</v>
       </c>
@@ -26652,7 +26652,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A592" s="59" t="s">
         <v>295</v>
       </c>
@@ -26681,7 +26681,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A593" s="59" t="s">
         <v>295</v>
       </c>
@@ -26710,7 +26710,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A594" s="59" t="s">
         <v>295</v>
       </c>
@@ -26739,7 +26739,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A595" s="59" t="s">
         <v>295</v>
       </c>
@@ -26768,7 +26768,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A596" s="59" t="s">
         <v>295</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A597" s="59" t="s">
         <v>295</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A598" s="59" t="s">
         <v>295</v>
       </c>
@@ -26855,7 +26855,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A599" s="59" t="s">
         <v>295</v>
       </c>
@@ -26884,7 +26884,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A600" s="59" t="s">
         <v>295</v>
       </c>
@@ -26913,7 +26913,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A601" s="59" t="s">
         <v>295</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
       <c r="A602" s="59" t="s">
         <v>295</v>
       </c>
@@ -26995,33 +26995,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2FB926-1F0A-48DA-A285-A57511180878}">
   <dimension ref="A1:AF61"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" style="59" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.26953125" style="59" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" style="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="59" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="13.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" style="59" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="13.7265625" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1328125" style="59" customWidth="1"/>
+    <col min="14" max="14" width="13.7265625" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.7109375" style="59"/>
+    <col min="18" max="19" width="8.7265625" style="59"/>
     <col min="20" max="20" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="8.7109375" style="59"/>
-    <col min="24" max="24" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.5703125" style="59" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" style="59" customWidth="1"/>
+    <col min="21" max="23" width="8.7265625" style="59"/>
+    <col min="24" max="24" width="9.86328125" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" style="59" customWidth="1"/>
+    <col min="26" max="26" width="17.7265625" style="59" customWidth="1"/>
     <col min="27" max="27" width="11" style="59" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="8.7109375" style="59"/>
+    <col min="29" max="30" width="8.7265625" style="59"/>
     <col min="31" max="32" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7109375" style="59"/>
-    <col min="34" max="34" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="59"/>
+    <col min="33" max="33" width="8.7265625" style="59"/>
+    <col min="34" max="34" width="9.86328125" style="59" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.7265625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="59" t="s">
         <v>289</v>
       </c>
@@ -27029,7 +27029,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="59" t="s">
         <v>291</v>
       </c>
@@ -27037,7 +27037,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="59" t="s">
         <v>292</v>
       </c>
@@ -27045,7 +27045,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="59" t="s">
         <v>316</v>
       </c>
@@ -27053,7 +27053,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="59" t="s">
         <v>318</v>
       </c>
@@ -27073,7 +27073,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="60" t="s">
         <v>298</v>
       </c>
@@ -27096,7 +27096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="60" t="s">
         <v>305</v>
       </c>
@@ -27119,7 +27119,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="60" t="s">
         <v>304</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="60" t="s">
         <v>306</v>
       </c>
@@ -27165,7 +27165,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="60" t="s">
         <v>307</v>
       </c>
@@ -27185,7 +27185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="60" t="s">
         <v>308</v>
       </c>
@@ -27208,7 +27208,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="60" t="s">
         <v>309</v>
       </c>
@@ -27231,7 +27231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="60" t="s">
         <v>310</v>
       </c>
@@ -27254,7 +27254,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="60" t="s">
         <v>259</v>
       </c>
@@ -27274,7 +27274,7 @@
         <v>-1020.6999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="60" t="s">
         <v>319</v>
       </c>
@@ -27294,7 +27294,7 @@
         <v>-2041.4</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A18" s="60" t="s">
         <v>321</v>
       </c>
@@ -27315,12 +27315,12 @@
         <v>-368.4</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A20" s="61" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A21" s="61"/>
       <c r="B21" s="59" t="s">
         <v>322</v>
@@ -27348,7 +27348,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B22" s="59">
         <v>2025</v>
       </c>
@@ -27416,7 +27416,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A23" s="59">
         <v>5</v>
       </c>
@@ -27512,7 +27512,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A24" s="59">
         <v>20</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>3.3612076852699002</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A25" s="59">
         <v>35</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A26" s="59">
         <v>50</v>
       </c>
@@ -27770,7 +27770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A27" s="59">
         <v>100</v>
       </c>
@@ -27850,7 +27850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.75">
       <c r="AD28" s="59" t="s">
         <v>328</v>
       </c>
@@ -27863,12 +27863,12 @@
         <v>19061207685269.898</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A29" s="61" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A30" s="61"/>
       <c r="B30" s="59" t="s">
         <v>322</v>
@@ -27896,7 +27896,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B31" s="59">
         <v>2025</v>
       </c>
@@ -27964,7 +27964,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A32" s="59">
         <v>5</v>
       </c>
@@ -28060,7 +28060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A33" s="59">
         <v>20</v>
       </c>
@@ -28157,7 +28157,7 @@
         <v>8.4544130073085526</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A34" s="59">
         <v>35</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A35" s="59">
         <v>50</v>
       </c>
@@ -28350,7 +28350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A36" s="59">
         <v>100</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A37" s="61"/>
       <c r="AD37" s="59" t="s">
         <v>328</v>
@@ -28452,12 +28452,12 @@
         <v>8454413007308.5527</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A38" s="61" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B39" s="59">
         <v>2021</v>
       </c>
@@ -28549,7 +28549,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A40" s="59" t="s">
         <v>279</v>
       </c>
@@ -28644,7 +28644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A41" s="59" t="s">
         <v>3</v>
       </c>
@@ -28754,15 +28754,15 @@
         <v>10179858186482.16</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A42" s="61"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A43" s="61" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.75">
       <c r="B44" s="59">
         <v>2021</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A45" s="59" t="s">
         <v>279</v>
       </c>
@@ -28979,7 +28979,7 @@
         <v>82349999999999.906</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A46" s="59" t="s">
         <v>3</v>
       </c>
@@ -29104,12 +29104,12 @@
         <v>175050000000000.19</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.75">
       <c r="A48" s="61" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.75">
       <c r="B49" s="59">
         <v>2021</v>
       </c>
@@ -29201,65 +29201,65 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A50" s="59" t="s">
         <v>279</v>
       </c>
       <c r="B50" s="59">
-        <f>B45-B40</f>
+        <f>B45</f>
         <v>11739999999999.781</v>
       </c>
       <c r="C50" s="59">
-        <f t="shared" ref="C50:AE50" si="11">C45-C40</f>
+        <f t="shared" ref="C50:AE50" si="11">C45</f>
         <v>15479999999999.563</v>
       </c>
       <c r="D50" s="59">
         <f t="shared" si="11"/>
-        <v>14262590618336.266</v>
+        <v>19219999999999.344</v>
       </c>
       <c r="E50" s="59">
         <f t="shared" si="11"/>
-        <v>14033160980809.359</v>
+        <v>22959999999999.125</v>
       </c>
       <c r="F50" s="59">
         <f t="shared" si="11"/>
-        <v>14496695095948.611</v>
+        <v>26699999999999.816</v>
       </c>
       <c r="G50" s="59">
         <f t="shared" si="11"/>
-        <v>15055622905878.521</v>
+        <v>30439999999999.602</v>
       </c>
       <c r="H50" s="59">
         <f t="shared" si="11"/>
-        <v>16601801705756.383</v>
+        <v>34179999999999.383</v>
       </c>
       <c r="I50" s="59">
-        <f>I45-I40</f>
-        <v>20460858208954.422</v>
+        <f t="shared" si="11"/>
+        <v>37919999999999.164</v>
       </c>
       <c r="J50" s="59">
         <f t="shared" si="11"/>
-        <v>25844434968016.004</v>
+        <v>41659999999998.945</v>
       </c>
       <c r="K50" s="59">
         <f t="shared" si="11"/>
-        <v>30604344349679.773</v>
+        <v>45399999999999.633</v>
       </c>
       <c r="L50" s="59">
         <f t="shared" si="11"/>
-        <v>36888773987206.344</v>
+        <v>49139999999999.414</v>
       </c>
       <c r="M50" s="59">
         <f t="shared" si="11"/>
-        <v>42901321961619.672</v>
+        <v>52879999999999.203</v>
       </c>
       <c r="N50" s="59">
         <f t="shared" si="11"/>
-        <v>49967547974412.633</v>
+        <v>56619999999998.984</v>
       </c>
       <c r="O50" s="59">
         <f t="shared" si="11"/>
-        <v>57033773987206.492</v>
+        <v>60359999999999.672</v>
       </c>
       <c r="P50" s="59">
         <f t="shared" si="11"/>
@@ -29326,16 +29326,16 @@
         <v>82349999999999.906</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A51" s="59" t="s">
         <v>3</v>
       </c>
       <c r="B51" s="59">
-        <f>B46-B41</f>
+        <f>B46</f>
         <v>0</v>
       </c>
       <c r="C51" s="59">
-        <f t="shared" ref="C51:AE51" si="12">C46-C41</f>
+        <f t="shared" ref="C51:AE51" si="12">C46</f>
         <v>990000000001.60071</v>
       </c>
       <c r="D51" s="59">
@@ -29356,107 +29356,107 @@
       </c>
       <c r="H51" s="59">
         <f t="shared" si="12"/>
-        <v>47331706754978.016</v>
+        <v>47840000000000.148</v>
       </c>
       <c r="I51" s="59">
         <f t="shared" si="12"/>
-        <v>50156465242279.828</v>
+        <v>57209999999999.125</v>
       </c>
       <c r="J51" s="59">
         <f t="shared" si="12"/>
-        <v>56400141813519.594</v>
+        <v>66580000000001.75</v>
       </c>
       <c r="K51" s="59">
         <f t="shared" si="12"/>
-        <v>65770141813518.578</v>
+        <v>75950000000000.734</v>
       </c>
       <c r="L51" s="59">
         <f t="shared" si="12"/>
-        <v>75140141813517.547</v>
+        <v>85319999999999.703</v>
       </c>
       <c r="M51" s="59">
         <f t="shared" si="12"/>
-        <v>84510141813520.172</v>
+        <v>94690000000002.328</v>
       </c>
       <c r="N51" s="59">
         <f t="shared" si="12"/>
-        <v>93880141813519.156</v>
+        <v>104060000000001.31</v>
       </c>
       <c r="O51" s="59">
         <f t="shared" si="12"/>
-        <v>103250141813518.14</v>
+        <v>113430000000000.3</v>
       </c>
       <c r="P51" s="59">
         <f t="shared" si="12"/>
-        <v>112620141813517.11</v>
+        <v>122799999999999.27</v>
       </c>
       <c r="Q51" s="59">
         <f t="shared" si="12"/>
-        <v>116160141813517.98</v>
+        <v>126340000000000.14</v>
       </c>
       <c r="R51" s="59">
         <f t="shared" si="12"/>
-        <v>119700141813517.95</v>
+        <v>129880000000000.11</v>
       </c>
       <c r="S51" s="59">
         <f t="shared" si="12"/>
-        <v>123240141813517.92</v>
+        <v>133420000000000.08</v>
       </c>
       <c r="T51" s="59">
         <f t="shared" si="12"/>
-        <v>126780141813517.88</v>
+        <v>136960000000000.03</v>
       </c>
       <c r="U51" s="59">
         <f t="shared" si="12"/>
-        <v>130320141813517.84</v>
+        <v>140500000000000</v>
       </c>
       <c r="V51" s="59">
         <f t="shared" si="12"/>
-        <v>133860141813517.81</v>
+        <v>144039999999999.97</v>
       </c>
       <c r="W51" s="59">
         <f t="shared" si="12"/>
-        <v>137400141813517.78</v>
+        <v>147579999999999.94</v>
       </c>
       <c r="X51" s="59">
         <f t="shared" si="12"/>
-        <v>140940141813517.75</v>
+        <v>151119999999999.91</v>
       </c>
       <c r="Y51" s="59">
         <f t="shared" si="12"/>
-        <v>144480141813517.69</v>
+        <v>154659999999999.84</v>
       </c>
       <c r="Z51" s="59">
         <f t="shared" si="12"/>
-        <v>148020141813517.66</v>
+        <v>158199999999999.81</v>
       </c>
       <c r="AA51" s="59">
         <f t="shared" si="12"/>
-        <v>151390141813518.47</v>
+        <v>161570000000000.63</v>
       </c>
       <c r="AB51" s="59">
         <f t="shared" si="12"/>
-        <v>154760141813518.34</v>
+        <v>164940000000000.5</v>
       </c>
       <c r="AC51" s="59">
         <f t="shared" si="12"/>
-        <v>158130141813518.25</v>
+        <v>168310000000000.41</v>
       </c>
       <c r="AD51" s="59">
         <f t="shared" si="12"/>
-        <v>161500141813518.13</v>
+        <v>171680000000000.28</v>
       </c>
       <c r="AE51" s="59">
         <f t="shared" si="12"/>
-        <v>164870141813518.03</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+        <v>175050000000000.19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A53" s="61" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.75">
       <c r="B54" s="59">
         <v>2021</v>
       </c>
@@ -29548,7 +29548,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A55" s="59" t="s">
         <v>279</v>
       </c>
@@ -29562,51 +29562,51 @@
       </c>
       <c r="D55" s="66">
         <f>D50/CApULAbIFM!$B$2</f>
-        <v>9508393.7455575112</v>
+        <v>12813333.333332896</v>
       </c>
       <c r="E55" s="66">
         <f>E50/CApULAbIFM!$B$2</f>
-        <v>9355440.6538729072</v>
+        <v>15306666.666666083</v>
       </c>
       <c r="F55" s="66">
         <f>F50/CApULAbIFM!$B$2</f>
-        <v>9664463.3972990736</v>
+        <v>17799999.999999877</v>
       </c>
       <c r="G55" s="66">
         <f>G50/CApULAbIFM!$B$2</f>
-        <v>10037081.937252348</v>
+        <v>20293333.333333068</v>
       </c>
       <c r="H55" s="66">
         <f>H50/CApULAbIFM!$B$2</f>
-        <v>11067867.803837588</v>
+        <v>22786666.666666254</v>
       </c>
       <c r="I55" s="66">
         <f>I50/CApULAbIFM!$B$2</f>
-        <v>13640572.139302948</v>
+        <v>25279999.999999441</v>
       </c>
       <c r="J55" s="66">
         <f>J50/CApULAbIFM!$B$2</f>
-        <v>17229623.312010668</v>
+        <v>27773333.333332632</v>
       </c>
       <c r="K55" s="66">
         <f>K50/CApULAbIFM!$B$2</f>
-        <v>20402896.233119849</v>
+        <v>30266666.666666422</v>
       </c>
       <c r="L55" s="66">
         <f>L50/CApULAbIFM!$B$2</f>
-        <v>24592515.991470896</v>
+        <v>32759999.999999609</v>
       </c>
       <c r="M55" s="66">
         <f>M50/CApULAbIFM!$B$2</f>
-        <v>28600881.307746448</v>
+        <v>35253333.333332799</v>
       </c>
       <c r="N55" s="66">
         <f>N50/CApULAbIFM!$B$2</f>
-        <v>33311698.649608422</v>
+        <v>37746666.666665986</v>
       </c>
       <c r="O55" s="66">
         <f>O50/CApULAbIFM!$B$2</f>
-        <v>38022515.991470993</v>
+        <v>40239999.999999784</v>
       </c>
       <c r="P55" s="66">
         <f>P50/CApULAbIFM!$B$2</f>
@@ -29673,7 +29673,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A56" s="59" t="s">
         <v>3</v>
       </c>
@@ -29703,107 +29703,107 @@
       </c>
       <c r="H56" s="59">
         <f>H51/TNC_summary!$C$10</f>
-        <v>23988937.516587194</v>
+        <v>24246553.726331349</v>
       </c>
       <c r="I56" s="59">
         <f>I51/TNC_summary!$C$10</f>
-        <v>25420598.436868832</v>
+        <v>28995512.93234513</v>
       </c>
       <c r="J56" s="59">
         <f>J51/TNC_summary!$C$10</f>
-        <v>28585055.782905638</v>
+        <v>33744472.138360754</v>
       </c>
       <c r="K56" s="59">
         <f>K51/TNC_summary!$C$10</f>
-        <v>33334014.988919422</v>
+        <v>38493431.344374537</v>
       </c>
       <c r="L56" s="59">
         <f>L51/TNC_summary!$C$10</f>
-        <v>38082974.194933198</v>
+        <v>43242390.550388314</v>
       </c>
       <c r="M56" s="59">
         <f>M51/TNC_summary!$C$10</f>
-        <v>42831933.40094883</v>
+        <v>47991349.756403945</v>
       </c>
       <c r="N56" s="59">
         <f>N51/TNC_summary!$C$10</f>
-        <v>47580892.606962614</v>
+        <v>52740308.962417729</v>
       </c>
       <c r="O56" s="59">
         <f>O51/TNC_summary!$C$10</f>
-        <v>52329851.812976398</v>
+        <v>57489268.168431513</v>
       </c>
       <c r="P56" s="59">
         <f>P51/TNC_summary!$C$10</f>
-        <v>57078811.018990166</v>
+        <v>62238227.374445289</v>
       </c>
       <c r="Q56" s="59">
         <f>Q51/TNC_summary!$C$10</f>
-        <v>58872974.902586199</v>
+        <v>64032391.258041315</v>
       </c>
       <c r="R56" s="59">
         <f>R51/TNC_summary!$C$10</f>
-        <v>60667138.786181763</v>
+        <v>65826555.141636886</v>
       </c>
       <c r="S56" s="59">
         <f>S51/TNC_summary!$C$10</f>
-        <v>62461302.669777334</v>
+        <v>67620719.025232449</v>
       </c>
       <c r="T56" s="59">
         <f>T51/TNC_summary!$C$10</f>
-        <v>64255466.55337289</v>
+        <v>69414882.908828005</v>
       </c>
       <c r="U56" s="59">
         <f>U51/TNC_summary!$C$10</f>
-        <v>66049630.436968461</v>
+        <v>71209046.792423576</v>
       </c>
       <c r="V56" s="59">
         <f>V51/TNC_summary!$C$10</f>
-        <v>67843794.320564032</v>
+        <v>73003210.676019147</v>
       </c>
       <c r="W56" s="59">
         <f>W51/TNC_summary!$C$10</f>
-        <v>69637958.204159588</v>
+        <v>74797374.559614718</v>
       </c>
       <c r="X56" s="59">
         <f>X51/TNC_summary!$C$10</f>
-        <v>71432122.087755159</v>
+        <v>76591538.443210274</v>
       </c>
       <c r="Y56" s="59">
         <f>Y51/TNC_summary!$C$10</f>
-        <v>73226285.971350715</v>
+        <v>78385702.32680583</v>
       </c>
       <c r="Z56" s="59">
         <f>Z51/TNC_summary!$C$10</f>
-        <v>75020449.854946285</v>
+        <v>80179866.210401401</v>
       </c>
       <c r="AA56" s="59">
         <f>AA51/TNC_summary!$C$10</f>
-        <v>76728453.326053217</v>
+        <v>81887869.681508347</v>
       </c>
       <c r="AB56" s="59">
         <f>AB51/TNC_summary!$C$10</f>
-        <v>78436456.797159687</v>
+        <v>83595873.152614802</v>
       </c>
       <c r="AC56" s="59">
         <f>AC51/TNC_summary!$C$10</f>
-        <v>80144460.268266171</v>
+        <v>85303876.623721287</v>
       </c>
       <c r="AD56" s="59">
         <f>AD51/TNC_summary!$C$10</f>
-        <v>81852463.739372641</v>
+        <v>87011880.094827756</v>
       </c>
       <c r="AE56" s="59">
         <f>AE51/TNC_summary!$C$10</f>
-        <v>83560467.210479125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+        <v>88719883.565934241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A58" s="61" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.75">
       <c r="B59" s="59">
         <v>2021</v>
       </c>
@@ -29895,7 +29895,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A60" s="59" t="s">
         <v>279</v>
       </c>
@@ -29909,51 +29909,51 @@
       </c>
       <c r="D60" s="66">
         <f t="shared" si="13"/>
-        <v>9508393.7455575112</v>
+        <v>12813333.333332896</v>
       </c>
       <c r="E60" s="66">
         <f t="shared" si="13"/>
-        <v>9355440.6538729072</v>
+        <v>15306666.666666083</v>
       </c>
       <c r="F60" s="66">
         <f t="shared" si="13"/>
-        <v>9664463.3972990736</v>
+        <v>17799999.999999877</v>
       </c>
       <c r="G60" s="66">
         <f t="shared" si="13"/>
-        <v>10037081.937252348</v>
+        <v>20293333.333333068</v>
       </c>
       <c r="H60" s="66">
         <f t="shared" si="13"/>
-        <v>11067867.803837588</v>
+        <v>22786666.666666254</v>
       </c>
       <c r="I60" s="66">
         <f>I55</f>
-        <v>13640572.139302948</v>
+        <v>25279999.999999441</v>
       </c>
       <c r="J60" s="66">
         <f t="shared" si="13"/>
-        <v>17229623.312010668</v>
+        <v>27773333.333332632</v>
       </c>
       <c r="K60" s="66">
         <f t="shared" si="13"/>
-        <v>20402896.233119849</v>
+        <v>30266666.666666422</v>
       </c>
       <c r="L60" s="66">
         <f t="shared" si="13"/>
-        <v>24592515.991470896</v>
+        <v>32759999.999999609</v>
       </c>
       <c r="M60" s="66">
         <f t="shared" si="13"/>
-        <v>28600881.307746448</v>
+        <v>35253333.333332799</v>
       </c>
       <c r="N60" s="66">
         <f t="shared" si="13"/>
-        <v>33311698.649608422</v>
+        <v>37746666.666665986</v>
       </c>
       <c r="O60" s="66">
         <f t="shared" si="13"/>
-        <v>38022515.991470993</v>
+        <v>40239999.999999784</v>
       </c>
       <c r="P60" s="66">
         <f t="shared" si="13"/>
@@ -30020,7 +30020,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A61" s="59" t="s">
         <v>3</v>
       </c>
@@ -30050,15 +30050,15 @@
       </c>
       <c r="H61" s="59">
         <f t="shared" si="14"/>
-        <v>4491342.9962696284</v>
+        <v>4748959.2060137838</v>
       </c>
       <c r="I61" s="59">
         <f t="shared" si="14"/>
-        <v>1431660.9202816375</v>
+        <v>4748959.2060137801</v>
       </c>
       <c r="J61" s="59">
         <f t="shared" si="14"/>
-        <v>3164457.3460368067</v>
+        <v>4748959.2060156241</v>
       </c>
       <c r="K61" s="59">
         <f t="shared" si="14"/>
@@ -30082,19 +30082,19 @@
       </c>
       <c r="P61" s="59">
         <f t="shared" si="14"/>
-        <v>4748959.2060137689</v>
+        <v>4748959.2060137764</v>
       </c>
       <c r="Q61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835960329</v>
+        <v>1794163.8835960254</v>
       </c>
       <c r="R61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955635</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="S61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955709</v>
+        <v>1794163.8835955635</v>
       </c>
       <c r="T61" s="59">
         <f t="shared" si="14"/>
@@ -30110,11 +30110,11 @@
       </c>
       <c r="W61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.883595556</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="X61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955709</v>
+        <v>1794163.883595556</v>
       </c>
       <c r="Y61" s="59">
         <f t="shared" si="14"/>
@@ -30126,11 +30126,11 @@
       </c>
       <c r="AA61" s="59">
         <f t="shared" si="14"/>
-        <v>1708003.4711069316</v>
+        <v>1708003.4711069465</v>
       </c>
       <c r="AB61" s="59">
         <f t="shared" si="14"/>
-        <v>1708003.4711064696</v>
+        <v>1708003.4711064547</v>
       </c>
       <c r="AC61" s="59">
         <f t="shared" si="14"/>
@@ -30153,17 +30153,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171879A6-D0D6-49AA-B160-18EBF002316C}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B1" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>335</v>
       </c>
@@ -30172,7 +30172,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>336</v>
       </c>
@@ -30180,7 +30180,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>338</v>
       </c>
@@ -30193,72 +30193,72 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0FF694-673B-4399-A04F-DA1E9EEB856B}">
   <dimension ref="A1:EC52"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="16" x14ac:dyDescent="0.8"/>
   <cols>
-    <col min="1" max="2" width="11.5703125" style="10"/>
-    <col min="3" max="3" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="16" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="16" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" style="16" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="11.54296875" style="10"/>
+    <col min="3" max="3" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="16" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.86328125" style="16" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.86328125" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.86328125" style="16" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="16" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="16" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" style="37" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="10" hidden="1" customWidth="1"/>
-    <col min="16" max="18" width="13.5703125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" style="16" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="13.54296875" style="16" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="16.1328125" style="37" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" style="10" hidden="1" customWidth="1"/>
+    <col min="16" max="18" width="13.54296875" style="10" customWidth="1"/>
     <col min="19" max="19" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="20" max="21" width="11.7109375" style="10" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" style="16" customWidth="1"/>
-    <col min="23" max="23" width="11.7109375" style="10" hidden="1" customWidth="1"/>
+    <col min="20" max="21" width="11.7265625" style="10" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="15.26953125" style="16" customWidth="1"/>
+    <col min="23" max="23" width="11.7265625" style="10" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="11.7109375" style="10" hidden="1" customWidth="1"/>
+    <col min="25" max="26" width="11.7265625" style="10" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="16" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="10" hidden="1" customWidth="1"/>
-    <col min="29" max="31" width="11.7109375" style="10" customWidth="1"/>
-    <col min="32" max="41" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="11.7109375" style="10" customWidth="1"/>
-    <col min="44" max="44" width="13.85546875" style="38" customWidth="1"/>
-    <col min="45" max="51" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7265625" style="10" hidden="1" customWidth="1"/>
+    <col min="29" max="31" width="11.7265625" style="10" customWidth="1"/>
+    <col min="32" max="41" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="11.7265625" style="10" customWidth="1"/>
+    <col min="44" max="44" width="13.86328125" style="38" customWidth="1"/>
+    <col min="45" max="51" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="55" max="57" width="11.7109375" style="10" customWidth="1"/>
-    <col min="58" max="67" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.5703125" style="10"/>
+    <col min="55" max="57" width="11.7265625" style="10" customWidth="1"/>
+    <col min="58" max="67" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.54296875" style="10"/>
     <col min="69" max="72" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="11.5703125" style="10"/>
+    <col min="73" max="73" width="11.54296875" style="10"/>
     <col min="74" max="77" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="11.5703125" style="10"/>
-    <col min="79" max="82" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="11.5703125" style="10"/>
-    <col min="84" max="87" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.54296875" style="10"/>
+    <col min="79" max="82" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="11.54296875" style="10"/>
+    <col min="84" max="87" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
     <col min="89" max="90" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="15.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="15.86328125" style="10" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="94" max="95" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="98" max="100" width="11.7109375" style="10" customWidth="1"/>
-    <col min="101" max="101" width="11.5703125" style="10"/>
-    <col min="102" max="103" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="11.5703125" style="10"/>
-    <col min="107" max="108" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="111" max="113" width="11.7109375" style="10" customWidth="1"/>
-    <col min="114" max="114" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="115" max="123" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="125" max="133" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="134" max="16384" width="11.5703125" style="10"/>
+    <col min="93" max="93" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="94" max="95" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="98" max="100" width="11.7265625" style="10" customWidth="1"/>
+    <col min="101" max="101" width="11.54296875" style="10"/>
+    <col min="102" max="103" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="11.54296875" style="10"/>
+    <col min="107" max="108" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="111" max="113" width="11.7265625" style="10" customWidth="1"/>
+    <col min="114" max="114" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="115" max="123" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="125" max="133" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="134" max="16384" width="11.54296875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:133" x14ac:dyDescent="0.8">
       <c r="F1" s="10"/>
       <c r="G1" s="10" t="s">
         <v>59</v>
@@ -30351,7 +30351,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:133" x14ac:dyDescent="0.8">
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
@@ -30396,7 +30396,7 @@
       <c r="DH2" s="15"/>
       <c r="DI2" s="15"/>
     </row>
-    <row r="3" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A3" s="10" t="s">
         <v>71</v>
       </c>
@@ -30797,7 +30797,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
@@ -31177,7 +31177,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="5" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
@@ -31557,7 +31557,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="6" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
@@ -31937,7 +31937,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="7" spans="1:133" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:133" s="16" customFormat="1" x14ac:dyDescent="0.8">
       <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
@@ -32344,7 +32344,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="8" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
@@ -32745,7 +32745,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="9" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
@@ -33146,7 +33146,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="10" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
@@ -33547,7 +33547,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="11" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -33927,7 +33927,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="12" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A12" s="10" t="s">
         <v>17</v>
       </c>
@@ -34307,7 +34307,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="13" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
@@ -34687,7 +34687,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="14" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A14" s="10" t="s">
         <v>19</v>
       </c>
@@ -35067,7 +35067,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="15" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A15" s="10" t="s">
         <v>21</v>
       </c>
@@ -35447,7 +35447,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="16" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A16" s="10" t="s">
         <v>16</v>
       </c>
@@ -35827,7 +35827,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
@@ -36207,7 +36207,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="18" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A18" s="10" t="s">
         <v>20</v>
       </c>
@@ -36587,7 +36587,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="19" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -36967,7 +36967,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="20" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A20" s="10" t="s">
         <v>29</v>
       </c>
@@ -37347,7 +37347,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="21" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A21" s="10" t="s">
         <v>26</v>
       </c>
@@ -37748,7 +37748,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="22" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
@@ -38149,7 +38149,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="23" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
@@ -38529,7 +38529,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="24" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A24" s="10" t="s">
         <v>34</v>
       </c>
@@ -38930,7 +38930,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="25" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A25" s="10" t="s">
         <v>24</v>
       </c>
@@ -39310,7 +39310,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="26" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A26" s="10" t="s">
         <v>37</v>
       </c>
@@ -39690,7 +39690,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="27" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
@@ -40070,7 +40070,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="28" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A28" s="10" t="s">
         <v>36</v>
       </c>
@@ -40450,7 +40450,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="29" spans="1:133" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:133" s="12" customFormat="1" x14ac:dyDescent="0.8">
       <c r="A29" s="24" t="s">
         <v>39</v>
       </c>
@@ -40841,7 +40841,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="30" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A30" s="10" t="s">
         <v>40</v>
       </c>
@@ -41221,7 +41221,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="31" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A31" s="10" t="s">
         <v>43</v>
       </c>
@@ -41622,7 +41622,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="32" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A32" s="10" t="s">
         <v>42</v>
       </c>
@@ -42002,7 +42002,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="33" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A33" s="10" t="s">
         <v>46</v>
       </c>
@@ -42403,7 +42403,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="34" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A34" s="10" t="s">
         <v>27</v>
       </c>
@@ -42804,7 +42804,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="35" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A35" s="10" t="s">
         <v>33</v>
       </c>
@@ -43184,7 +43184,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="36" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A36" s="10" t="s">
         <v>48</v>
       </c>
@@ -43564,7 +43564,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="37" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A37" s="10" t="s">
         <v>30</v>
       </c>
@@ -43944,7 +43944,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="38" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A38" s="10" t="s">
         <v>45</v>
       </c>
@@ -44345,7 +44345,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="39" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A39" s="10" t="s">
         <v>50</v>
       </c>
@@ -44725,7 +44725,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="40" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A40" s="10" t="s">
         <v>52</v>
       </c>
@@ -45126,7 +45126,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="41" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A41" s="10" t="s">
         <v>35</v>
       </c>
@@ -45506,7 +45506,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="42" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A42" s="10" t="s">
         <v>47</v>
       </c>
@@ -45886,7 +45886,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="43" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A43" s="10" t="s">
         <v>38</v>
       </c>
@@ -46266,7 +46266,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="44" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A44" s="10" t="s">
         <v>41</v>
       </c>
@@ -46646,7 +46646,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="45" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A45" s="10" t="s">
         <v>49</v>
       </c>
@@ -47026,7 +47026,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="46" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A46" s="10" t="s">
         <v>54</v>
       </c>
@@ -47427,7 +47427,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="47" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A47" s="10" t="s">
         <v>44</v>
       </c>
@@ -47828,7 +47828,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="48" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A48" s="10" t="s">
         <v>51</v>
       </c>
@@ -48229,7 +48229,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="49" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A49" s="10" t="s">
         <v>56</v>
       </c>
@@ -48609,7 +48609,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="50" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A50" s="10" t="s">
         <v>55</v>
       </c>
@@ -48989,7 +48989,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="51" spans="1:133" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:133" x14ac:dyDescent="0.8">
       <c r="A51" s="10" t="s">
         <v>53</v>
       </c>
@@ -49369,7 +49369,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="52" spans="1:133" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:133" s="30" customFormat="1" x14ac:dyDescent="0.8">
       <c r="A52" s="29" t="s">
         <v>239</v>
       </c>
@@ -49568,13 +49568,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59812A91-DF51-48C6-9139-7A65100E3E7B}">
   <dimension ref="A2:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="46.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.1328125" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B2" s="39" t="s">
         <v>244</v>
       </c>
@@ -49599,7 +49599,7 @@
       <c r="U2" s="40"/>
       <c r="V2" s="40"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B3" s="40" t="s">
         <v>245</v>
       </c>
@@ -49624,12 +49624,12 @@
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B4" s="8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>247</v>
       </c>
@@ -49637,7 +49637,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>249</v>
       </c>
@@ -49649,7 +49649,7 @@
         <v>252444615.67210001</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -49661,7 +49661,7 @@
         <v>127945483.62911001</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B9" s="8" t="s">
         <v>253</v>
       </c>
@@ -49670,7 +49670,7 @@
         <v>3554041.2119197226</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B10" s="8" t="s">
         <v>332</v>
       </c>
@@ -49679,7 +49679,7 @@
         <v>1973063.9059045622</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>247</v>
       </c>
@@ -49687,7 +49687,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>249</v>
       </c>
@@ -49699,7 +49699,7 @@
         <v>37999999.998844996</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -49711,7 +49711,7 @@
         <v>6764601.5311640995</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B15" s="8" t="s">
         <v>253</v>
       </c>
@@ -49720,7 +49720,7 @@
         <v>187905.59808789165</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.75">
       <c r="B16" s="8" t="s">
         <v>332</v>
       </c>
@@ -49729,11 +49729,11 @@
         <v>5617477.9584253943</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B17" s="8"/>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>247</v>
       </c>
@@ -49741,7 +49741,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>249</v>
       </c>
@@ -49753,7 +49753,7 @@
         <v>116013193.64404109</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -49765,7 +49765,7 @@
         <v>6813914.8343433412</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B21" s="8" t="s">
         <v>253</v>
       </c>
@@ -49774,7 +49774,7 @@
         <v>189275.41206509282</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B22" s="8" t="s">
         <v>332</v>
       </c>
@@ -49791,17 +49791,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3877CA7D-439B-4474-847A-349C8907D325}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="8" t="s">
         <v>256</v>
       </c>
@@ -49809,7 +49809,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>255</v>
       </c>
@@ -49818,7 +49818,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A5" s="44" t="s">
         <v>258</v>
       </c>
@@ -49826,7 +49826,7 @@
         <v>890909</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" s="44" t="s">
         <v>259</v>
       </c>
@@ -49835,7 +49835,7 @@
         <v>3390909</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A8" s="44" t="s">
         <v>260</v>
       </c>
@@ -49855,15 +49855,15 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:BL66"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="73.85546875" customWidth="1"/>
+    <col min="1" max="1" width="73.86328125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.1328125" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="45" t="s">
         <v>269</v>
       </c>
@@ -49931,17 +49931,17 @@
       <c r="BK1" s="47"/>
       <c r="BL1" s="47"/>
     </row>
-    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="48" t="s">
         <v>270</v>
       </c>
       <c r="B2" s="49"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
     </row>
-    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="45" t="s">
         <v>271</v>
       </c>
@@ -50009,7 +50009,7 @@
       <c r="BK4" s="47"/>
       <c r="BL4" s="47"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A5" s="50" t="s">
         <v>272</v>
       </c>
@@ -50017,15 +50017,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A6" s="50"/>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A7" s="50" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A8" s="53" t="s">
         <v>274</v>
       </c>
@@ -50037,7 +50037,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A9" s="53" t="s">
         <v>276</v>
       </c>
@@ -50049,7 +50049,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A10" s="53" t="s">
         <v>277</v>
       </c>
@@ -50061,7 +50061,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A11" s="53" t="s">
         <v>278</v>
       </c>
@@ -50073,7 +50073,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A12" s="53" t="s">
         <v>280</v>
       </c>
@@ -50085,7 +50085,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A13" s="53" t="s">
         <v>280</v>
       </c>
@@ -50097,7 +50097,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A14" s="53" t="s">
         <v>280</v>
       </c>
@@ -50109,7 +50109,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A15" s="53" t="s">
         <v>280</v>
       </c>
@@ -50121,7 +50121,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A16" s="53" t="s">
         <v>281</v>
       </c>
@@ -50133,7 +50133,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A17" s="53" t="s">
         <v>280</v>
       </c>
@@ -50145,7 +50145,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A18" s="53" t="s">
         <v>282</v>
       </c>
@@ -50157,7 +50157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A19" s="53" t="s">
         <v>283</v>
       </c>
@@ -50169,13 +50169,13 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A21" s="52" t="s">
         <v>351</v>
       </c>
       <c r="B21" s="51"/>
     </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A22" s="53" t="s">
         <v>279</v>
       </c>
@@ -50184,7 +50184,7 @@
         <v>102049999.99999999</v>
       </c>
     </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A23" s="53" t="s">
         <v>3</v>
       </c>
@@ -50193,15 +50193,15 @@
         <v>117750000</v>
       </c>
     </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A27" s="50"/>
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
@@ -50267,7 +50267,7 @@
       <c r="BK27" s="49"/>
       <c r="BL27" s="49"/>
     </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -50333,7 +50333,7 @@
       <c r="BK28" s="49"/>
       <c r="BL28" s="49"/>
     </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
       <c r="C29" s="49"/>
@@ -50399,7 +50399,7 @@
       <c r="BK29" s="55"/>
       <c r="BL29" s="55"/>
     </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
@@ -50465,7 +50465,7 @@
       <c r="BK30" s="49"/>
       <c r="BL30" s="49"/>
     </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -50531,7 +50531,7 @@
       <c r="BK31" s="49"/>
       <c r="BL31" s="49"/>
     </row>
-    <row r="32" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -50597,7 +50597,7 @@
       <c r="BK32" s="49"/>
       <c r="BL32" s="49"/>
     </row>
-    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -50663,7 +50663,7 @@
       <c r="BK33" s="49"/>
       <c r="BL33" s="49"/>
     </row>
-    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
@@ -50729,7 +50729,7 @@
       <c r="BK34" s="49"/>
       <c r="BL34" s="49"/>
     </row>
-    <row r="35" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -50795,7 +50795,7 @@
       <c r="BK35" s="49"/>
       <c r="BL35" s="49"/>
     </row>
-    <row r="36" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
@@ -50861,7 +50861,7 @@
       <c r="BK36" s="49"/>
       <c r="BL36" s="49"/>
     </row>
-    <row r="37" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
@@ -50927,20 +50927,20 @@
       <c r="BK37" s="49"/>
       <c r="BL37" s="49"/>
     </row>
-    <row r="39" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A39" s="49"/>
       <c r="B39" s="55"/>
     </row>
-    <row r="40" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A40" s="49"/>
       <c r="B40" s="55"/>
       <c r="D40" s="54"/>
     </row>
-    <row r="42" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A42" s="49"/>
       <c r="B42" s="56"/>
     </row>
-    <row r="43" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A43" s="50"/>
       <c r="B43" s="49"/>
       <c r="C43" s="49"/>
@@ -51006,7 +51006,7 @@
       <c r="BK43" s="49"/>
       <c r="BL43" s="49"/>
     </row>
-    <row r="44" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A44" s="50"/>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
@@ -51072,7 +51072,7 @@
       <c r="BK44" s="49"/>
       <c r="BL44" s="49"/>
     </row>
-    <row r="45" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
       <c r="C45" s="49"/>
@@ -51138,7 +51138,7 @@
       <c r="BK45" s="49"/>
       <c r="BL45" s="49"/>
     </row>
-    <row r="46" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>
@@ -51204,7 +51204,7 @@
       <c r="BK46" s="55"/>
       <c r="BL46" s="55"/>
     </row>
-    <row r="47" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
       <c r="C47" s="49"/>
@@ -51270,7 +51270,7 @@
       <c r="BK47" s="49"/>
       <c r="BL47" s="49"/>
     </row>
-    <row r="48" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
       <c r="C48" s="49"/>
@@ -51336,7 +51336,7 @@
       <c r="BK48" s="49"/>
       <c r="BL48" s="49"/>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
       <c r="C49" s="49"/>
@@ -51402,7 +51402,7 @@
       <c r="BK49" s="49"/>
       <c r="BL49" s="49"/>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
       <c r="C50" s="49"/>
@@ -51468,7 +51468,7 @@
       <c r="BK50" s="49"/>
       <c r="BL50" s="49"/>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
       <c r="C51" s="49"/>
@@ -51534,7 +51534,7 @@
       <c r="BK51" s="49"/>
       <c r="BL51" s="49"/>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
       <c r="C52" s="49"/>
@@ -51600,7 +51600,7 @@
       <c r="BK52" s="49"/>
       <c r="BL52" s="49"/>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A53" s="49"/>
       <c r="B53" s="49"/>
       <c r="C53" s="49"/>
@@ -51666,7 +51666,7 @@
       <c r="BK53" s="49"/>
       <c r="BL53" s="49"/>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A54" s="49"/>
       <c r="B54" s="49"/>
       <c r="C54" s="49"/>
@@ -51732,25 +51732,25 @@
       <c r="BK54" s="49"/>
       <c r="BL54" s="49"/>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A56" s="49"/>
       <c r="B56" s="55"/>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A57" s="49"/>
       <c r="B57" s="55"/>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A59" s="49"/>
       <c r="B59" s="57"/>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A61" s="50"/>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.75">
       <c r="A62" s="50"/>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.75">
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
@@ -51780,7 +51780,7 @@
       <c r="AE63" s="6"/>
       <c r="AF63" s="6"/>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.75">
       <c r="D64" s="55"/>
       <c r="E64" s="55"/>
       <c r="F64" s="55"/>
@@ -51811,7 +51811,7 @@
       <c r="AE64" s="55"/>
       <c r="AF64" s="55"/>
     </row>
-    <row r="65" spans="4:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:32" x14ac:dyDescent="0.75">
       <c r="D65" s="55"/>
       <c r="E65" s="55"/>
       <c r="F65" s="55"/>
@@ -51842,7 +51842,7 @@
       <c r="AE65" s="55"/>
       <c r="AF65" s="55"/>
     </row>
-    <row r="66" spans="4:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:32" x14ac:dyDescent="0.75">
       <c r="D66" s="55"/>
       <c r="E66" s="55"/>
       <c r="F66" s="55"/>
@@ -51885,13 +51885,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="31" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="2" max="31" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -51986,7 +51986,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -52081,7 +52081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -52111,15 +52111,15 @@
       </c>
       <c r="H3" s="3">
         <f>'EPA land and ag calcs'!H61</f>
-        <v>4491342.9962696284</v>
+        <v>4748959.2060137838</v>
       </c>
       <c r="I3" s="3">
         <f>'EPA land and ag calcs'!I61</f>
-        <v>1431660.9202816375</v>
+        <v>4748959.2060137801</v>
       </c>
       <c r="J3" s="3">
         <f>'EPA land and ag calcs'!J61</f>
-        <v>3164457.3460368067</v>
+        <v>4748959.2060156241</v>
       </c>
       <c r="K3" s="3">
         <f>'EPA land and ag calcs'!K61</f>
@@ -52143,19 +52143,19 @@
       </c>
       <c r="P3" s="3">
         <f>'EPA land and ag calcs'!P61</f>
-        <v>4748959.2060137689</v>
+        <v>4748959.2060137764</v>
       </c>
       <c r="Q3" s="3">
         <f>'EPA land and ag calcs'!Q61</f>
-        <v>1794163.8835960329</v>
+        <v>1794163.8835960254</v>
       </c>
       <c r="R3" s="3">
         <f>'EPA land and ag calcs'!R61</f>
-        <v>1794163.8835955635</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="S3" s="3">
         <f>'EPA land and ag calcs'!S61</f>
-        <v>1794163.8835955709</v>
+        <v>1794163.8835955635</v>
       </c>
       <c r="T3" s="3">
         <f>'EPA land and ag calcs'!T61</f>
@@ -52171,11 +52171,11 @@
       </c>
       <c r="W3" s="3">
         <f>'EPA land and ag calcs'!W61</f>
-        <v>1794163.883595556</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="X3" s="3">
         <f>'EPA land and ag calcs'!X61</f>
-        <v>1794163.8835955709</v>
+        <v>1794163.883595556</v>
       </c>
       <c r="Y3" s="3">
         <f>'EPA land and ag calcs'!Y61</f>
@@ -52187,11 +52187,11 @@
       </c>
       <c r="AA3" s="3">
         <f>'EPA land and ag calcs'!AA61</f>
-        <v>1708003.4711069316</v>
+        <v>1708003.4711069465</v>
       </c>
       <c r="AB3" s="3">
         <f>'EPA land and ag calcs'!AB61</f>
-        <v>1708003.4711064696</v>
+        <v>1708003.4711064547</v>
       </c>
       <c r="AC3" s="3">
         <f>'EPA land and ag calcs'!AC61</f>
@@ -52206,7 +52206,7 @@
         <v>1708003.4711064845</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -52220,51 +52220,51 @@
       </c>
       <c r="D4" s="3">
         <f>'EPA land and ag calcs'!D60</f>
-        <v>9508393.7455575112</v>
+        <v>12813333.333332896</v>
       </c>
       <c r="E4" s="3">
         <f>'EPA land and ag calcs'!E60</f>
-        <v>9355440.6538729072</v>
+        <v>15306666.666666083</v>
       </c>
       <c r="F4" s="3">
         <f>'EPA land and ag calcs'!F60</f>
-        <v>9664463.3972990736</v>
+        <v>17799999.999999877</v>
       </c>
       <c r="G4" s="3">
         <f>'EPA land and ag calcs'!G60</f>
-        <v>10037081.937252348</v>
+        <v>20293333.333333068</v>
       </c>
       <c r="H4" s="3">
         <f>'EPA land and ag calcs'!H60</f>
-        <v>11067867.803837588</v>
+        <v>22786666.666666254</v>
       </c>
       <c r="I4" s="3">
         <f>'EPA land and ag calcs'!I60</f>
-        <v>13640572.139302948</v>
+        <v>25279999.999999441</v>
       </c>
       <c r="J4" s="3">
         <f>'EPA land and ag calcs'!J60</f>
-        <v>17229623.312010668</v>
+        <v>27773333.333332632</v>
       </c>
       <c r="K4" s="3">
         <f>'EPA land and ag calcs'!K60</f>
-        <v>20402896.233119849</v>
+        <v>30266666.666666422</v>
       </c>
       <c r="L4" s="3">
         <f>'EPA land and ag calcs'!L60</f>
-        <v>24592515.991470896</v>
+        <v>32759999.999999609</v>
       </c>
       <c r="M4" s="3">
         <f>'EPA land and ag calcs'!M60</f>
-        <v>28600881.307746448</v>
+        <v>35253333.333332799</v>
       </c>
       <c r="N4" s="3">
         <f>'EPA land and ag calcs'!N60</f>
-        <v>33311698.649608422</v>
+        <v>37746666.666665986</v>
       </c>
       <c r="O4" s="3">
         <f>'EPA land and ag calcs'!O60</f>
-        <v>38022515.991470993</v>
+        <v>40239999.999999784</v>
       </c>
       <c r="P4" s="3">
         <f>'EPA land and ag calcs'!P60</f>
@@ -52331,7 +52331,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -52426,7 +52426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A6" s="58" t="s">
         <v>6</v>
       </c>
@@ -52550,7 +52550,7 @@
         <v>116927.89655172414</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
       <c r="A7" s="58" t="s">
         <v>7</v>
       </c>

--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\land\PLANAbPiaSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\land\PLANAbPiaSY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891FB75-0F32-495E-81CB-E9AA727372B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD6CD2D-AE1B-423B-9A95-7F3C436C29B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId10"/>
+    <pivotCache cacheId="18" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -8245,7 +8245,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F9A18EA-B1D4-4240-B553-42848006A3CE}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F9A18EA-B1D4-4240-B553-42848006A3CE}" name="PivotTable2" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:F16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -8668,18 +8668,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="75.26953125" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" customWidth="1"/>
+    <col min="2" max="2" width="75.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -8687,130 +8687,130 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>2016</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>355</v>
       </c>
@@ -8829,14 +8829,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34DB6CD0-7C30-4BD3-9788-250A76B3BC98}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K602"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="11.40625" style="59"/>
-    <col min="5" max="5" width="18.26953125" style="59" customWidth="1"/>
-    <col min="6" max="16384" width="11.40625" style="59"/>
+    <col min="1" max="4" width="11.42578125" style="59"/>
+    <col min="5" max="5" width="18.28515625" style="59" customWidth="1"/>
+    <col min="6" max="16384" width="11.42578125" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:11" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
         <v>285</v>
       </c>
@@ -8849,7 +8849,7 @@
       <c r="H1" s="67"/>
       <c r="I1" s="67"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
         <v>286</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>295</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
         <v>295</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
         <v>295</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
         <v>295</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
         <v>295</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
         <v>295</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
         <v>295</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
         <v>295</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
         <v>295</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
         <v>295</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
         <v>295</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="s">
         <v>295</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
         <v>295</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="s">
         <v>295</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
         <v>295</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59" t="s">
         <v>295</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
         <v>295</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
         <v>295</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="59" t="s">
         <v>295</v>
       </c>
@@ -9476,7 +9476,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="59" t="s">
         <v>295</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="59" t="s">
         <v>295</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
         <v>295</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="59" t="s">
         <v>295</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
         <v>295</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59" t="s">
         <v>295</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="59" t="s">
         <v>295</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="59" t="s">
         <v>295</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="s">
         <v>295</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="s">
         <v>295</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="59" t="s">
         <v>295</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="59" t="s">
         <v>295</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="59" t="s">
         <v>295</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="59" t="s">
         <v>295</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="59" t="s">
         <v>295</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="59" t="s">
         <v>295</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="s">
         <v>295</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="59" t="s">
         <v>295</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59" t="s">
         <v>295</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="59" t="s">
         <v>295</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="59" t="s">
         <v>295</v>
       </c>
@@ -10137,7 +10137,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="59" t="s">
         <v>295</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="59" t="s">
         <v>295</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="s">
         <v>295</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="59" t="s">
         <v>295</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="59" t="s">
         <v>295</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>295</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>295</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>295</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>295</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>295</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>295</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>295</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
         <v>295</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="59" t="s">
         <v>295</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="59" t="s">
         <v>295</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="59" t="s">
         <v>295</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="59" t="s">
         <v>295</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="59" t="s">
         <v>295</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="59" t="s">
         <v>295</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="59" t="s">
         <v>295</v>
       </c>
@@ -10756,7 +10756,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="59" t="s">
         <v>295</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="59" t="s">
         <v>295</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="59" t="s">
         <v>295</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="59" t="s">
         <v>295</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="59" t="s">
         <v>295</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="59" t="s">
         <v>295</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="59" t="s">
         <v>295</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="59" t="s">
         <v>295</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="59" t="s">
         <v>295</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="59" t="s">
         <v>295</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="59" t="s">
         <v>295</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="59" t="s">
         <v>295</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="59" t="s">
         <v>295</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="59" t="s">
         <v>295</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="59" t="s">
         <v>295</v>
       </c>
@@ -11231,7 +11231,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="59" t="s">
         <v>295</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="59" t="s">
         <v>295</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="59" t="s">
         <v>295</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="59" t="s">
         <v>295</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="59" t="s">
         <v>295</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="59" t="s">
         <v>295</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="59" t="s">
         <v>295</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="59" t="s">
         <v>295</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59" t="s">
         <v>295</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="59" t="s">
         <v>295</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="59" t="s">
         <v>295</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="59" t="s">
         <v>295</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="59" t="s">
         <v>295</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="59" t="s">
         <v>295</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="59" t="s">
         <v>295</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="59" t="s">
         <v>295</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="59" t="s">
         <v>295</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="59" t="s">
         <v>295</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="59" t="s">
         <v>295</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="59" t="s">
         <v>295</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="59" t="s">
         <v>295</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="59" t="s">
         <v>295</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="59" t="s">
         <v>295</v>
       </c>
@@ -11926,7 +11926,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="59" t="s">
         <v>295</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="59" t="s">
         <v>295</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="59" t="s">
         <v>295</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="59" t="s">
         <v>295</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="59" t="s">
         <v>295</v>
       </c>
@@ -12071,7 +12071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="59" t="s">
         <v>295</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="59" t="s">
         <v>295</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="59" t="s">
         <v>295</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59" t="s">
         <v>295</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="59" t="s">
         <v>295</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="59" t="s">
         <v>295</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="59" t="s">
         <v>295</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="59" t="s">
         <v>295</v>
       </c>
@@ -12303,7 +12303,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="59" t="s">
         <v>295</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="59" t="s">
         <v>295</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="59" t="s">
         <v>295</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="59" t="s">
         <v>295</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="59" t="s">
         <v>295</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="59" t="s">
         <v>295</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="59" t="s">
         <v>295</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="59" t="s">
         <v>295</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="59" t="s">
         <v>295</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="59" t="s">
         <v>295</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="59" t="s">
         <v>295</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="59" t="s">
         <v>295</v>
       </c>
@@ -12651,7 +12651,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="59" t="s">
         <v>295</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="59" t="s">
         <v>295</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="59" t="s">
         <v>295</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="59" t="s">
         <v>295</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="59" t="s">
         <v>295</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="59" t="s">
         <v>295</v>
       </c>
@@ -12825,7 +12825,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="59" t="s">
         <v>295</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="59" t="s">
         <v>295</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="59" t="s">
         <v>295</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="59" t="s">
         <v>295</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="59" t="s">
         <v>295</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="59" t="s">
         <v>295</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="59" t="s">
         <v>295</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="59" t="s">
         <v>295</v>
       </c>
@@ -13057,7 +13057,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="59" t="s">
         <v>295</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="59" t="s">
         <v>295</v>
       </c>
@@ -13115,7 +13115,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="59" t="s">
         <v>295</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="59" t="s">
         <v>295</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="59" t="s">
         <v>295</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="59" t="s">
         <v>295</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="59" t="s">
         <v>295</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="59" t="s">
         <v>295</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="59" t="s">
         <v>295</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="59" t="s">
         <v>295</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="59" t="s">
         <v>295</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="59" t="s">
         <v>295</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="59" t="s">
         <v>295</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="59" t="s">
         <v>295</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="59" t="s">
         <v>295</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="59" t="s">
         <v>295</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="59" t="s">
         <v>295</v>
       </c>
@@ -13558,7 +13558,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="59" t="s">
         <v>295</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="59" t="s">
         <v>295</v>
       </c>
@@ -13616,7 +13616,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="59" t="s">
         <v>295</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="59" t="s">
         <v>295</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="59" t="s">
         <v>295</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="59" t="s">
         <v>295</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="59" t="s">
         <v>295</v>
       </c>
@@ -13781,7 +13781,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="59" t="s">
         <v>295</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="59" t="s">
         <v>295</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="59" t="s">
         <v>295</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="59" t="s">
         <v>295</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="59" t="s">
         <v>295</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="59" t="s">
         <v>295</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="59" t="s">
         <v>295</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="59" t="s">
         <v>295</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="59" t="s">
         <v>295</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="59" t="s">
         <v>295</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="59" t="s">
         <v>295</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="59" t="s">
         <v>295</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="59" t="s">
         <v>295</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="59" t="s">
         <v>295</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="59" t="s">
         <v>295</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="59" t="s">
         <v>295</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="59" t="s">
         <v>295</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="59" t="s">
         <v>295</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="59" t="s">
         <v>295</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="59" t="s">
         <v>295</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="59" t="s">
         <v>295</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="59" t="s">
         <v>295</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="59" t="s">
         <v>295</v>
       </c>
@@ -14500,7 +14500,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="59" t="s">
         <v>295</v>
       </c>
@@ -14529,7 +14529,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="59" t="s">
         <v>295</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="59" t="s">
         <v>295</v>
       </c>
@@ -14591,7 +14591,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="59" t="s">
         <v>295</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="59" t="s">
         <v>295</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="59" t="s">
         <v>295</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="59" t="s">
         <v>295</v>
       </c>
@@ -14723,7 +14723,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="59" t="s">
         <v>295</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="59" t="s">
         <v>295</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="59" t="s">
         <v>295</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="59" t="s">
         <v>295</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="59" t="s">
         <v>295</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="59" t="s">
         <v>295</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="59" t="s">
         <v>295</v>
       </c>
@@ -14932,7 +14932,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="59" t="s">
         <v>295</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="59" t="s">
         <v>295</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="59" t="s">
         <v>295</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="59" t="s">
         <v>295</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="59" t="s">
         <v>295</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="59" t="s">
         <v>295</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="59" t="s">
         <v>295</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="59" t="s">
         <v>295</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="59" t="s">
         <v>295</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="59" t="s">
         <v>295</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="59" t="s">
         <v>295</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="59" t="s">
         <v>295</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="59" t="s">
         <v>295</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="59" t="s">
         <v>295</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="59" t="s">
         <v>295</v>
       </c>
@@ -15407,7 +15407,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="59" t="s">
         <v>295</v>
       </c>
@@ -15436,7 +15436,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="59" t="s">
         <v>295</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="59" t="s">
         <v>295</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="59" t="s">
         <v>295</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="59" t="s">
         <v>295</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="59" t="s">
         <v>295</v>
       </c>
@@ -15593,7 +15593,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="59" t="s">
         <v>295</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="59" t="s">
         <v>295</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="59" t="s">
         <v>295</v>
       </c>
@@ -15692,7 +15692,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="59" t="s">
         <v>295</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="59" t="s">
         <v>295</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="59" t="s">
         <v>295</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="59" t="s">
         <v>295</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="59" t="s">
         <v>295</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="59" t="s">
         <v>295</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="59" t="s">
         <v>295</v>
       </c>
@@ -15907,7 +15907,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="59" t="s">
         <v>295</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="59" t="s">
         <v>295</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="59" t="s">
         <v>295</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="59" t="s">
         <v>295</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="59" t="s">
         <v>295</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="59" t="s">
         <v>295</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="59" t="s">
         <v>295</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="59" t="s">
         <v>295</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="59" t="s">
         <v>295</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="59" t="s">
         <v>295</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="59" t="s">
         <v>295</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="59" t="s">
         <v>295</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="59" t="s">
         <v>295</v>
       </c>
@@ -16308,7 +16308,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="59" t="s">
         <v>295</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="59" t="s">
         <v>295</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="59" t="s">
         <v>295</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="59" t="s">
         <v>295</v>
       </c>
@@ -16424,7 +16424,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="59" t="s">
         <v>295</v>
       </c>
@@ -16453,7 +16453,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="59" t="s">
         <v>295</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="59" t="s">
         <v>295</v>
       </c>
@@ -16511,7 +16511,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="59" t="s">
         <v>295</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="59" t="s">
         <v>295</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="59" t="s">
         <v>295</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="59" t="s">
         <v>295</v>
       </c>
@@ -16627,7 +16627,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="59" t="s">
         <v>295</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="59" t="s">
         <v>295</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="59" t="s">
         <v>295</v>
       </c>
@@ -16714,7 +16714,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="59" t="s">
         <v>295</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="59" t="s">
         <v>295</v>
       </c>
@@ -16772,7 +16772,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="59" t="s">
         <v>295</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="59" t="s">
         <v>295</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="59" t="s">
         <v>295</v>
       </c>
@@ -16859,7 +16859,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="59" t="s">
         <v>295</v>
       </c>
@@ -16888,7 +16888,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="59" t="s">
         <v>295</v>
       </c>
@@ -16917,7 +16917,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="59" t="s">
         <v>295</v>
       </c>
@@ -16946,7 +16946,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="59" t="s">
         <v>295</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="59" t="s">
         <v>295</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="59" t="s">
         <v>295</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="59" t="s">
         <v>295</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="59" t="s">
         <v>295</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="59" t="s">
         <v>295</v>
       </c>
@@ -17120,7 +17120,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="59" t="s">
         <v>295</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="59" t="s">
         <v>295</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="59" t="s">
         <v>295</v>
       </c>
@@ -17207,7 +17207,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="59" t="s">
         <v>295</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="59" t="s">
         <v>295</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="59" t="s">
         <v>295</v>
       </c>
@@ -17294,7 +17294,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="59" t="s">
         <v>295</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="59" t="s">
         <v>295</v>
       </c>
@@ -17352,7 +17352,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="59" t="s">
         <v>295</v>
       </c>
@@ -17381,7 +17381,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="59" t="s">
         <v>295</v>
       </c>
@@ -17410,7 +17410,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="59" t="s">
         <v>295</v>
       </c>
@@ -17439,7 +17439,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="59" t="s">
         <v>295</v>
       </c>
@@ -17468,7 +17468,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="59" t="s">
         <v>295</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="59" t="s">
         <v>295</v>
       </c>
@@ -17526,7 +17526,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="59" t="s">
         <v>295</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="59" t="s">
         <v>295</v>
       </c>
@@ -17584,7 +17584,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="59" t="s">
         <v>295</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="59" t="s">
         <v>295</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="59" t="s">
         <v>295</v>
       </c>
@@ -17671,7 +17671,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="59" t="s">
         <v>295</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="59" t="s">
         <v>295</v>
       </c>
@@ -17729,7 +17729,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="59" t="s">
         <v>295</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="59" t="s">
         <v>295</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="59" t="s">
         <v>295</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="59" t="s">
         <v>295</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="59" t="s">
         <v>295</v>
       </c>
@@ -17874,7 +17874,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="59" t="s">
         <v>295</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="59" t="s">
         <v>295</v>
       </c>
@@ -17932,7 +17932,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="59" t="s">
         <v>295</v>
       </c>
@@ -17961,7 +17961,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="59" t="s">
         <v>295</v>
       </c>
@@ -17990,7 +17990,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="59" t="s">
         <v>295</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="59" t="s">
         <v>295</v>
       </c>
@@ -18048,7 +18048,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="59" t="s">
         <v>295</v>
       </c>
@@ -18077,7 +18077,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="59" t="s">
         <v>295</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="59" t="s">
         <v>295</v>
       </c>
@@ -18139,7 +18139,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="59" t="s">
         <v>295</v>
       </c>
@@ -18172,7 +18172,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="59" t="s">
         <v>295</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="59" t="s">
         <v>295</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="59" t="s">
         <v>295</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="59" t="s">
         <v>295</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="59" t="s">
         <v>295</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="59" t="s">
         <v>295</v>
       </c>
@@ -18354,7 +18354,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="59" t="s">
         <v>295</v>
       </c>
@@ -18383,7 +18383,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="59" t="s">
         <v>295</v>
       </c>
@@ -18412,7 +18412,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="59" t="s">
         <v>295</v>
       </c>
@@ -18445,7 +18445,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="59" t="s">
         <v>295</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="59" t="s">
         <v>295</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="59" t="s">
         <v>295</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="59" t="s">
         <v>295</v>
       </c>
@@ -18573,7 +18573,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="59" t="s">
         <v>295</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="59" t="s">
         <v>295</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="59" t="s">
         <v>295</v>
       </c>
@@ -18660,7 +18660,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="59" t="s">
         <v>295</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="59" t="s">
         <v>295</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="59" t="s">
         <v>295</v>
       </c>
@@ -18751,7 +18751,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="59" t="s">
         <v>295</v>
       </c>
@@ -18784,7 +18784,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="59" t="s">
         <v>295</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="59" t="s">
         <v>295</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="59" t="s">
         <v>295</v>
       </c>
@@ -18879,7 +18879,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="59" t="s">
         <v>295</v>
       </c>
@@ -18908,7 +18908,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="59" t="s">
         <v>295</v>
       </c>
@@ -18937,7 +18937,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="59" t="s">
         <v>295</v>
       </c>
@@ -18966,7 +18966,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="59" t="s">
         <v>295</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="59" t="s">
         <v>295</v>
       </c>
@@ -19024,7 +19024,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="59" t="s">
         <v>295</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="59" t="s">
         <v>295</v>
       </c>
@@ -19090,7 +19090,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="59" t="s">
         <v>295</v>
       </c>
@@ -19123,7 +19123,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="59" t="s">
         <v>295</v>
       </c>
@@ -19156,7 +19156,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="59" t="s">
         <v>295</v>
       </c>
@@ -19185,7 +19185,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="59" t="s">
         <v>295</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="59" t="s">
         <v>295</v>
       </c>
@@ -19240,7 +19240,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="59" t="s">
         <v>295</v>
       </c>
@@ -19269,7 +19269,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="59" t="s">
         <v>295</v>
       </c>
@@ -19298,7 +19298,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="59" t="s">
         <v>295</v>
       </c>
@@ -19327,7 +19327,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="59" t="s">
         <v>295</v>
       </c>
@@ -19357,7 +19357,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="59" t="s">
         <v>295</v>
       </c>
@@ -19390,7 +19390,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="59" t="s">
         <v>295</v>
       </c>
@@ -19423,7 +19423,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="59" t="s">
         <v>295</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="59" t="s">
         <v>295</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="59" t="s">
         <v>295</v>
       </c>
@@ -19511,7 +19511,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="59" t="s">
         <v>295</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="59" t="s">
         <v>295</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="59" t="s">
         <v>295</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="59" t="s">
         <v>295</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" s="59" t="s">
         <v>295</v>
       </c>
@@ -19660,7 +19660,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" s="59" t="s">
         <v>295</v>
       </c>
@@ -19693,7 +19693,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" s="59" t="s">
         <v>295</v>
       </c>
@@ -19726,7 +19726,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" s="59" t="s">
         <v>295</v>
       </c>
@@ -19759,7 +19759,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="59" t="s">
         <v>295</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="59" t="s">
         <v>295</v>
       </c>
@@ -19817,7 +19817,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="59" t="s">
         <v>295</v>
       </c>
@@ -19846,7 +19846,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="59" t="s">
         <v>295</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="59" t="s">
         <v>295</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="59" t="s">
         <v>295</v>
       </c>
@@ -19933,7 +19933,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" s="59" t="s">
         <v>295</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" s="59" t="s">
         <v>295</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" s="59" t="s">
         <v>295</v>
       </c>
@@ -20032,7 +20032,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" s="59" t="s">
         <v>295</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="59" t="s">
         <v>295</v>
       </c>
@@ -20094,7 +20094,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="59" t="s">
         <v>295</v>
       </c>
@@ -20123,7 +20123,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="59" t="s">
         <v>295</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="59" t="s">
         <v>295</v>
       </c>
@@ -20181,7 +20181,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="59" t="s">
         <v>295</v>
       </c>
@@ -20210,7 +20210,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="59" t="s">
         <v>295</v>
       </c>
@@ -20239,7 +20239,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" s="59" t="s">
         <v>295</v>
       </c>
@@ -20272,7 +20272,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" s="59" t="s">
         <v>295</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" s="59" t="s">
         <v>295</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" s="59" t="s">
         <v>295</v>
       </c>
@@ -20371,7 +20371,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="59" t="s">
         <v>295</v>
       </c>
@@ -20400,7 +20400,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="59" t="s">
         <v>295</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="59" t="s">
         <v>295</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="59" t="s">
         <v>295</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="59" t="s">
         <v>295</v>
       </c>
@@ -20516,7 +20516,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="59" t="s">
         <v>295</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="59" t="s">
         <v>295</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" s="59" t="s">
         <v>295</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" s="59" t="s">
         <v>295</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" s="59" t="s">
         <v>295</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" s="59" t="s">
         <v>295</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="59" t="s">
         <v>295</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="59" t="s">
         <v>295</v>
       </c>
@@ -20768,7 +20768,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="59" t="s">
         <v>295</v>
       </c>
@@ -20797,7 +20797,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="59" t="s">
         <v>295</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="59" t="s">
         <v>295</v>
       </c>
@@ -20855,7 +20855,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="59" t="s">
         <v>295</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="59" t="s">
         <v>295</v>
       </c>
@@ -20913,7 +20913,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="59" t="s">
         <v>295</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="59" t="s">
         <v>295</v>
       </c>
@@ -20971,7 +20971,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="59" t="s">
         <v>295</v>
       </c>
@@ -21000,7 +21000,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="59" t="s">
         <v>295</v>
       </c>
@@ -21029,7 +21029,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="59" t="s">
         <v>295</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="59" t="s">
         <v>295</v>
       </c>
@@ -21087,7 +21087,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="59" t="s">
         <v>295</v>
       </c>
@@ -21116,7 +21116,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="59" t="s">
         <v>295</v>
       </c>
@@ -21145,7 +21145,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="59" t="s">
         <v>295</v>
       </c>
@@ -21174,7 +21174,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="59" t="s">
         <v>295</v>
       </c>
@@ -21203,7 +21203,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="59" t="s">
         <v>295</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="59" t="s">
         <v>295</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="59" t="s">
         <v>295</v>
       </c>
@@ -21290,7 +21290,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="59" t="s">
         <v>295</v>
       </c>
@@ -21319,7 +21319,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="59" t="s">
         <v>295</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="59" t="s">
         <v>295</v>
       </c>
@@ -21377,7 +21377,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="59" t="s">
         <v>295</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="59" t="s">
         <v>295</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="59" t="s">
         <v>295</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="59" t="s">
         <v>295</v>
       </c>
@@ -21493,7 +21493,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="59" t="s">
         <v>295</v>
       </c>
@@ -21522,7 +21522,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="59" t="s">
         <v>295</v>
       </c>
@@ -21551,7 +21551,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="59" t="s">
         <v>295</v>
       </c>
@@ -21580,7 +21580,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="59" t="s">
         <v>295</v>
       </c>
@@ -21609,7 +21609,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="59" t="s">
         <v>295</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="59" t="s">
         <v>295</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="59" t="s">
         <v>295</v>
       </c>
@@ -21696,7 +21696,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="59" t="s">
         <v>295</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="59" t="s">
         <v>295</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="59" t="s">
         <v>295</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="59" t="s">
         <v>295</v>
       </c>
@@ -21812,7 +21812,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="59" t="s">
         <v>295</v>
       </c>
@@ -21841,7 +21841,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="59" t="s">
         <v>295</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="59" t="s">
         <v>295</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="59" t="s">
         <v>295</v>
       </c>
@@ -21928,7 +21928,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="59" t="s">
         <v>295</v>
       </c>
@@ -21957,7 +21957,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="59" t="s">
         <v>295</v>
       </c>
@@ -21986,7 +21986,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="59" t="s">
         <v>295</v>
       </c>
@@ -22015,7 +22015,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="59" t="s">
         <v>295</v>
       </c>
@@ -22044,7 +22044,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="59" t="s">
         <v>295</v>
       </c>
@@ -22073,7 +22073,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="59" t="s">
         <v>295</v>
       </c>
@@ -22102,7 +22102,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="59" t="s">
         <v>295</v>
       </c>
@@ -22131,7 +22131,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="59" t="s">
         <v>295</v>
       </c>
@@ -22160,7 +22160,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="59" t="s">
         <v>295</v>
       </c>
@@ -22189,7 +22189,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="59" t="s">
         <v>295</v>
       </c>
@@ -22218,7 +22218,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="59" t="s">
         <v>295</v>
       </c>
@@ -22247,7 +22247,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="59" t="s">
         <v>295</v>
       </c>
@@ -22276,7 +22276,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="59" t="s">
         <v>295</v>
       </c>
@@ -22305,7 +22305,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="59" t="s">
         <v>295</v>
       </c>
@@ -22334,7 +22334,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="59" t="s">
         <v>295</v>
       </c>
@@ -22363,7 +22363,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="59" t="s">
         <v>295</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="59" t="s">
         <v>295</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="59" t="s">
         <v>295</v>
       </c>
@@ -22450,7 +22450,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="59" t="s">
         <v>295</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="59" t="s">
         <v>295</v>
       </c>
@@ -22508,7 +22508,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="59" t="s">
         <v>295</v>
       </c>
@@ -22537,7 +22537,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="59" t="s">
         <v>295</v>
       </c>
@@ -22570,7 +22570,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="59" t="s">
         <v>295</v>
       </c>
@@ -22603,7 +22603,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" s="59" t="s">
         <v>295</v>
       </c>
@@ -22636,7 +22636,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" s="59" t="s">
         <v>295</v>
       </c>
@@ -22669,7 +22669,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="59" t="s">
         <v>295</v>
       </c>
@@ -22698,7 +22698,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="59" t="s">
         <v>295</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="59" t="s">
         <v>295</v>
       </c>
@@ -22756,7 +22756,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="59" t="s">
         <v>295</v>
       </c>
@@ -22785,7 +22785,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="59" t="s">
         <v>295</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="59" t="s">
         <v>295</v>
       </c>
@@ -22843,7 +22843,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" s="59" t="s">
         <v>295</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" s="59" t="s">
         <v>295</v>
       </c>
@@ -22909,7 +22909,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" s="59" t="s">
         <v>295</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" s="59" t="s">
         <v>295</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="59" t="s">
         <v>295</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="59" t="s">
         <v>295</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="59" t="s">
         <v>295</v>
       </c>
@@ -23062,7 +23062,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="59" t="s">
         <v>295</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="59" t="s">
         <v>295</v>
       </c>
@@ -23120,7 +23120,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="59" t="s">
         <v>295</v>
       </c>
@@ -23149,7 +23149,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" s="59" t="s">
         <v>295</v>
       </c>
@@ -23182,7 +23182,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" s="59" t="s">
         <v>295</v>
       </c>
@@ -23215,7 +23215,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" s="59" t="s">
         <v>295</v>
       </c>
@@ -23248,7 +23248,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" s="59" t="s">
         <v>295</v>
       </c>
@@ -23281,7 +23281,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="59" t="s">
         <v>295</v>
       </c>
@@ -23310,7 +23310,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="59" t="s">
         <v>295</v>
       </c>
@@ -23339,7 +23339,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="59" t="s">
         <v>295</v>
       </c>
@@ -23368,7 +23368,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="59" t="s">
         <v>295</v>
       </c>
@@ -23397,7 +23397,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="59" t="s">
         <v>295</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="59" t="s">
         <v>295</v>
       </c>
@@ -23455,7 +23455,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" s="59" t="s">
         <v>295</v>
       </c>
@@ -23488,7 +23488,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" s="59" t="s">
         <v>295</v>
       </c>
@@ -23521,7 +23521,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" s="59" t="s">
         <v>295</v>
       </c>
@@ -23554,7 +23554,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" s="59" t="s">
         <v>295</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="59" t="s">
         <v>295</v>
       </c>
@@ -23616,7 +23616,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="59" t="s">
         <v>295</v>
       </c>
@@ -23645,7 +23645,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="59" t="s">
         <v>295</v>
       </c>
@@ -23674,7 +23674,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="59" t="s">
         <v>295</v>
       </c>
@@ -23703,7 +23703,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="59" t="s">
         <v>295</v>
       </c>
@@ -23732,7 +23732,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="59" t="s">
         <v>295</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" s="59" t="s">
         <v>295</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" s="59" t="s">
         <v>295</v>
       </c>
@@ -23824,7 +23824,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="59" t="s">
         <v>295</v>
       </c>
@@ -23857,7 +23857,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="59" t="s">
         <v>295</v>
       </c>
@@ -23890,7 +23890,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="59" t="s">
         <v>295</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="59" t="s">
         <v>295</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="59" t="s">
         <v>295</v>
       </c>
@@ -23974,7 +23974,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="59" t="s">
         <v>295</v>
       </c>
@@ -24003,7 +24003,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="59" t="s">
         <v>295</v>
       </c>
@@ -24032,7 +24032,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="59" t="s">
         <v>295</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" s="59" t="s">
         <v>295</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" s="59" t="s">
         <v>295</v>
       </c>
@@ -24127,7 +24127,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" s="59" t="s">
         <v>295</v>
       </c>
@@ -24160,7 +24160,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" s="59" t="s">
         <v>295</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>forest management</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="59" t="s">
         <v>295</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="59" t="s">
         <v>295</v>
       </c>
@@ -24251,7 +24251,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="59" t="s">
         <v>295</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="59" t="s">
         <v>295</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="59" t="s">
         <v>295</v>
       </c>
@@ -24338,7 +24338,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="59" t="s">
         <v>295</v>
       </c>
@@ -24367,7 +24367,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" s="59" t="s">
         <v>295</v>
       </c>
@@ -24400,7 +24400,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" s="59" t="s">
         <v>295</v>
       </c>
@@ -24433,7 +24433,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" s="59" t="s">
         <v>295</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" s="59" t="s">
         <v>295</v>
       </c>
@@ -24499,7 +24499,7 @@
         <v>afforestation and reforestation</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="59" t="s">
         <v>295</v>
       </c>
@@ -24528,7 +24528,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="59" t="s">
         <v>295</v>
       </c>
@@ -24557,7 +24557,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="59" t="s">
         <v>295</v>
       </c>
@@ -24586,7 +24586,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="59" t="s">
         <v>295</v>
       </c>
@@ -24615,7 +24615,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="59" t="s">
         <v>295</v>
       </c>
@@ -24644,7 +24644,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="59" t="s">
         <v>295</v>
       </c>
@@ -24673,7 +24673,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" s="59" t="s">
         <v>295</v>
       </c>
@@ -24706,7 +24706,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" s="59" t="s">
         <v>295</v>
       </c>
@@ -24739,7 +24739,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" s="59" t="s">
         <v>295</v>
       </c>
@@ -24772,7 +24772,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" s="59" t="s">
         <v>295</v>
       </c>
@@ -24805,7 +24805,7 @@
         <v>*handled in agriculture files</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="59" t="s">
         <v>295</v>
       </c>
@@ -24834,7 +24834,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="59" t="s">
         <v>295</v>
       </c>
@@ -24863,7 +24863,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="59" t="s">
         <v>295</v>
       </c>
@@ -24892,7 +24892,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="59" t="s">
         <v>295</v>
       </c>
@@ -24921,7 +24921,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="59" t="s">
         <v>295</v>
       </c>
@@ -24950,7 +24950,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="59" t="s">
         <v>295</v>
       </c>
@@ -24979,7 +24979,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="59" t="s">
         <v>295</v>
       </c>
@@ -25008,7 +25008,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="59" t="s">
         <v>295</v>
       </c>
@@ -25037,7 +25037,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="59" t="s">
         <v>295</v>
       </c>
@@ -25066,7 +25066,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" s="59" t="s">
         <v>295</v>
       </c>
@@ -25099,7 +25099,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" s="59" t="s">
         <v>295</v>
       </c>
@@ -25132,7 +25132,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" s="59" t="s">
         <v>295</v>
       </c>
@@ -25165,7 +25165,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" s="59" t="s">
         <v>295</v>
       </c>
@@ -25198,7 +25198,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" s="59" t="s">
         <v>295</v>
       </c>
@@ -25231,7 +25231,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="59" t="s">
         <v>295</v>
       </c>
@@ -25260,7 +25260,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="59" t="s">
         <v>295</v>
       </c>
@@ -25289,7 +25289,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="59" t="s">
         <v>295</v>
       </c>
@@ -25318,7 +25318,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="59" t="s">
         <v>295</v>
       </c>
@@ -25347,7 +25347,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="59" t="s">
         <v>295</v>
       </c>
@@ -25376,7 +25376,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="59" t="s">
         <v>295</v>
       </c>
@@ -25405,7 +25405,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="59" t="s">
         <v>295</v>
       </c>
@@ -25434,7 +25434,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="59" t="s">
         <v>295</v>
       </c>
@@ -25463,7 +25463,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="59" t="s">
         <v>295</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="59" t="s">
         <v>295</v>
       </c>
@@ -25521,7 +25521,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="59" t="s">
         <v>295</v>
       </c>
@@ -25550,7 +25550,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="59" t="s">
         <v>295</v>
       </c>
@@ -25579,7 +25579,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="59" t="s">
         <v>295</v>
       </c>
@@ -25608,7 +25608,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="59" t="s">
         <v>295</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="59" t="s">
         <v>295</v>
       </c>
@@ -25666,7 +25666,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="59" t="s">
         <v>295</v>
       </c>
@@ -25695,7 +25695,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="59" t="s">
         <v>295</v>
       </c>
@@ -25724,7 +25724,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="59" t="s">
         <v>295</v>
       </c>
@@ -25753,7 +25753,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="59" t="s">
         <v>295</v>
       </c>
@@ -25782,7 +25782,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="59" t="s">
         <v>295</v>
       </c>
@@ -25811,7 +25811,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="59" t="s">
         <v>295</v>
       </c>
@@ -25840,7 +25840,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="59" t="s">
         <v>295</v>
       </c>
@@ -25869,7 +25869,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="59" t="s">
         <v>295</v>
       </c>
@@ -25898,7 +25898,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="59" t="s">
         <v>295</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="59" t="s">
         <v>295</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="59" t="s">
         <v>295</v>
       </c>
@@ -25985,7 +25985,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="59" t="s">
         <v>295</v>
       </c>
@@ -26014,7 +26014,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="59" t="s">
         <v>295</v>
       </c>
@@ -26043,7 +26043,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="59" t="s">
         <v>295</v>
       </c>
@@ -26072,7 +26072,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="59" t="s">
         <v>295</v>
       </c>
@@ -26101,7 +26101,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="59" t="s">
         <v>295</v>
       </c>
@@ -26130,7 +26130,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="59" t="s">
         <v>295</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="59" t="s">
         <v>295</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="59" t="s">
         <v>295</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="59" t="s">
         <v>295</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="59" t="s">
         <v>295</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="59" t="s">
         <v>295</v>
       </c>
@@ -26304,7 +26304,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="59" t="s">
         <v>295</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="59" t="s">
         <v>295</v>
       </c>
@@ -26362,7 +26362,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="59" t="s">
         <v>295</v>
       </c>
@@ -26391,7 +26391,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="59" t="s">
         <v>295</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="59" t="s">
         <v>295</v>
       </c>
@@ -26449,7 +26449,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="59" t="s">
         <v>295</v>
       </c>
@@ -26478,7 +26478,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="59" t="s">
         <v>295</v>
       </c>
@@ -26507,7 +26507,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="59" t="s">
         <v>295</v>
       </c>
@@ -26536,7 +26536,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="59" t="s">
         <v>295</v>
       </c>
@@ -26565,7 +26565,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="59" t="s">
         <v>295</v>
       </c>
@@ -26594,7 +26594,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="59" t="s">
         <v>295</v>
       </c>
@@ -26623,7 +26623,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="59" t="s">
         <v>295</v>
       </c>
@@ -26652,7 +26652,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="59" t="s">
         <v>295</v>
       </c>
@@ -26681,7 +26681,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="59" t="s">
         <v>295</v>
       </c>
@@ -26710,7 +26710,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="59" t="s">
         <v>295</v>
       </c>
@@ -26739,7 +26739,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="59" t="s">
         <v>295</v>
       </c>
@@ -26768,7 +26768,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="59" t="s">
         <v>295</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="59" t="s">
         <v>295</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="59" t="s">
         <v>295</v>
       </c>
@@ -26855,7 +26855,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="59" t="s">
         <v>295</v>
       </c>
@@ -26884,7 +26884,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="59" t="s">
         <v>295</v>
       </c>
@@ -26913,7 +26913,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="59" t="s">
         <v>295</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.75">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="59" t="s">
         <v>295</v>
       </c>
@@ -26995,33 +26995,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2FB926-1F0A-48DA-A285-A57511180878}">
   <dimension ref="A1:AF61"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" style="59" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" style="59" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="59" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="13.7265625" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1328125" style="59" customWidth="1"/>
-    <col min="14" max="14" width="13.7265625" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.54296875" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="13.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" style="59" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.5703125" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.7265625" style="59"/>
+    <col min="18" max="19" width="8.7109375" style="59"/>
     <col min="20" max="20" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="8.7265625" style="59"/>
-    <col min="24" max="24" width="9.86328125" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.54296875" style="59" customWidth="1"/>
-    <col min="26" max="26" width="17.7265625" style="59" customWidth="1"/>
+    <col min="21" max="23" width="8.7109375" style="59"/>
+    <col min="24" max="24" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.5703125" style="59" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" style="59" customWidth="1"/>
     <col min="27" max="27" width="11" style="59" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="8.7265625" style="59"/>
+    <col min="29" max="30" width="8.7109375" style="59"/>
     <col min="31" max="32" width="12" style="59" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.7265625" style="59"/>
-    <col min="34" max="34" width="9.86328125" style="59" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="8.7265625" style="59"/>
+    <col min="33" max="33" width="8.7109375" style="59"/>
+    <col min="34" max="34" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="59" t="s">
         <v>289</v>
       </c>
@@ -27029,7 +27029,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
         <v>291</v>
       </c>
@@ -27037,7 +27037,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>292</v>
       </c>
@@ -27045,7 +27045,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
         <v>316</v>
       </c>
@@ -27053,7 +27053,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
         <v>318</v>
       </c>
@@ -27073,7 +27073,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
         <v>298</v>
       </c>
@@ -27096,7 +27096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="60" t="s">
         <v>305</v>
       </c>
@@ -27119,7 +27119,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
         <v>304</v>
       </c>
@@ -27142,7 +27142,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
         <v>306</v>
       </c>
@@ -27165,7 +27165,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>307</v>
       </c>
@@ -27185,7 +27185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="60" t="s">
         <v>308</v>
       </c>
@@ -27208,7 +27208,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="s">
         <v>309</v>
       </c>
@@ -27231,7 +27231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="60" t="s">
         <v>310</v>
       </c>
@@ -27254,7 +27254,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
         <v>259</v>
       </c>
@@ -27274,7 +27274,7 @@
         <v>-1020.6999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="60" t="s">
         <v>319</v>
       </c>
@@ -27294,7 +27294,7 @@
         <v>-2041.4</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="60" t="s">
         <v>321</v>
       </c>
@@ -27315,12 +27315,12 @@
         <v>-368.4</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="61" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="59" t="s">
         <v>322</v>
@@ -27348,7 +27348,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B22" s="59">
         <v>2025</v>
       </c>
@@ -27416,7 +27416,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="59">
         <v>5</v>
       </c>
@@ -27512,7 +27512,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="59">
         <v>20</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>3.3612076852699002</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="59">
         <v>35</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="59">
         <v>50</v>
       </c>
@@ -27770,7 +27770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="59">
         <v>100</v>
       </c>
@@ -27850,7 +27850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AD28" s="59" t="s">
         <v>328</v>
       </c>
@@ -27863,12 +27863,12 @@
         <v>19061207685269.898</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="61" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="61"/>
       <c r="B30" s="59" t="s">
         <v>322</v>
@@ -27896,7 +27896,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B31" s="59">
         <v>2025</v>
       </c>
@@ -27964,7 +27964,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="59">
         <v>5</v>
       </c>
@@ -28060,7 +28060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="59">
         <v>20</v>
       </c>
@@ -28157,7 +28157,7 @@
         <v>8.4544130073085526</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="59">
         <v>35</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="59">
         <v>50</v>
       </c>
@@ -28350,7 +28350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="59">
         <v>100</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="AD37" s="59" t="s">
         <v>328</v>
@@ -28452,12 +28452,12 @@
         <v>8454413007308.5527</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="61" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B39" s="59">
         <v>2021</v>
       </c>
@@ -28549,7 +28549,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="59" t="s">
         <v>279</v>
       </c>
@@ -28644,7 +28644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="59" t="s">
         <v>3</v>
       </c>
@@ -28754,15 +28754,15 @@
         <v>10179858186482.16</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="61"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="61" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B44" s="59">
         <v>2021</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="s">
         <v>279</v>
       </c>
@@ -28979,7 +28979,7 @@
         <v>82349999999999.906</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="59" t="s">
         <v>3</v>
       </c>
@@ -29104,12 +29104,12 @@
         <v>175050000000000.19</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="61" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B49" s="59">
         <v>2021</v>
       </c>
@@ -29201,65 +29201,65 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>279</v>
       </c>
       <c r="B50" s="59">
-        <f>B45</f>
+        <f>B45-B40</f>
         <v>11739999999999.781</v>
       </c>
       <c r="C50" s="59">
-        <f t="shared" ref="C50:AE50" si="11">C45</f>
+        <f t="shared" ref="C50:AE50" si="11">C45-C40</f>
         <v>15479999999999.563</v>
       </c>
       <c r="D50" s="59">
         <f t="shared" si="11"/>
-        <v>19219999999999.344</v>
+        <v>14262590618336.266</v>
       </c>
       <c r="E50" s="59">
         <f t="shared" si="11"/>
-        <v>22959999999999.125</v>
+        <v>14033160980809.359</v>
       </c>
       <c r="F50" s="59">
         <f t="shared" si="11"/>
-        <v>26699999999999.816</v>
+        <v>14496695095948.611</v>
       </c>
       <c r="G50" s="59">
         <f t="shared" si="11"/>
-        <v>30439999999999.602</v>
+        <v>15055622905878.521</v>
       </c>
       <c r="H50" s="59">
         <f t="shared" si="11"/>
-        <v>34179999999999.383</v>
+        <v>16601801705756.383</v>
       </c>
       <c r="I50" s="59">
-        <f t="shared" si="11"/>
-        <v>37919999999999.164</v>
+        <f>I45-I40</f>
+        <v>20460858208954.422</v>
       </c>
       <c r="J50" s="59">
         <f t="shared" si="11"/>
-        <v>41659999999998.945</v>
+        <v>25844434968016.004</v>
       </c>
       <c r="K50" s="59">
         <f t="shared" si="11"/>
-        <v>45399999999999.633</v>
+        <v>30604344349679.773</v>
       </c>
       <c r="L50" s="59">
         <f t="shared" si="11"/>
-        <v>49139999999999.414</v>
+        <v>36888773987206.344</v>
       </c>
       <c r="M50" s="59">
         <f t="shared" si="11"/>
-        <v>52879999999999.203</v>
+        <v>42901321961619.672</v>
       </c>
       <c r="N50" s="59">
         <f t="shared" si="11"/>
-        <v>56619999999998.984</v>
+        <v>49967547974412.633</v>
       </c>
       <c r="O50" s="59">
         <f t="shared" si="11"/>
-        <v>60359999999999.672</v>
+        <v>57033773987206.492</v>
       </c>
       <c r="P50" s="59">
         <f t="shared" si="11"/>
@@ -29326,16 +29326,16 @@
         <v>82349999999999.906</v>
       </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>3</v>
       </c>
       <c r="B51" s="59">
-        <f>B46</f>
+        <f>B46-B41</f>
         <v>0</v>
       </c>
       <c r="C51" s="59">
-        <f t="shared" ref="C51:AE51" si="12">C46</f>
+        <f t="shared" ref="C51:AE51" si="12">C46-C41</f>
         <v>990000000001.60071</v>
       </c>
       <c r="D51" s="59">
@@ -29356,107 +29356,107 @@
       </c>
       <c r="H51" s="59">
         <f t="shared" si="12"/>
-        <v>47840000000000.148</v>
+        <v>47331706754978.016</v>
       </c>
       <c r="I51" s="59">
         <f t="shared" si="12"/>
-        <v>57209999999999.125</v>
+        <v>50156465242279.828</v>
       </c>
       <c r="J51" s="59">
         <f t="shared" si="12"/>
-        <v>66580000000001.75</v>
+        <v>56400141813519.594</v>
       </c>
       <c r="K51" s="59">
         <f t="shared" si="12"/>
-        <v>75950000000000.734</v>
+        <v>65770141813518.578</v>
       </c>
       <c r="L51" s="59">
         <f t="shared" si="12"/>
-        <v>85319999999999.703</v>
+        <v>75140141813517.547</v>
       </c>
       <c r="M51" s="59">
         <f t="shared" si="12"/>
-        <v>94690000000002.328</v>
+        <v>84510141813520.172</v>
       </c>
       <c r="N51" s="59">
         <f t="shared" si="12"/>
-        <v>104060000000001.31</v>
+        <v>93880141813519.156</v>
       </c>
       <c r="O51" s="59">
         <f t="shared" si="12"/>
-        <v>113430000000000.3</v>
+        <v>103250141813518.14</v>
       </c>
       <c r="P51" s="59">
         <f t="shared" si="12"/>
-        <v>122799999999999.27</v>
+        <v>112620141813517.11</v>
       </c>
       <c r="Q51" s="59">
         <f t="shared" si="12"/>
-        <v>126340000000000.14</v>
+        <v>116160141813517.98</v>
       </c>
       <c r="R51" s="59">
         <f t="shared" si="12"/>
-        <v>129880000000000.11</v>
+        <v>119700141813517.95</v>
       </c>
       <c r="S51" s="59">
         <f t="shared" si="12"/>
-        <v>133420000000000.08</v>
+        <v>123240141813517.92</v>
       </c>
       <c r="T51" s="59">
         <f t="shared" si="12"/>
-        <v>136960000000000.03</v>
+        <v>126780141813517.88</v>
       </c>
       <c r="U51" s="59">
         <f t="shared" si="12"/>
-        <v>140500000000000</v>
+        <v>130320141813517.84</v>
       </c>
       <c r="V51" s="59">
         <f t="shared" si="12"/>
-        <v>144039999999999.97</v>
+        <v>133860141813517.81</v>
       </c>
       <c r="W51" s="59">
         <f t="shared" si="12"/>
-        <v>147579999999999.94</v>
+        <v>137400141813517.78</v>
       </c>
       <c r="X51" s="59">
         <f t="shared" si="12"/>
-        <v>151119999999999.91</v>
+        <v>140940141813517.75</v>
       </c>
       <c r="Y51" s="59">
         <f t="shared" si="12"/>
-        <v>154659999999999.84</v>
+        <v>144480141813517.69</v>
       </c>
       <c r="Z51" s="59">
         <f t="shared" si="12"/>
-        <v>158199999999999.81</v>
+        <v>148020141813517.66</v>
       </c>
       <c r="AA51" s="59">
         <f t="shared" si="12"/>
-        <v>161570000000000.63</v>
+        <v>151390141813518.47</v>
       </c>
       <c r="AB51" s="59">
         <f t="shared" si="12"/>
-        <v>164940000000000.5</v>
+        <v>154760141813518.34</v>
       </c>
       <c r="AC51" s="59">
         <f t="shared" si="12"/>
-        <v>168310000000000.41</v>
+        <v>158130141813518.25</v>
       </c>
       <c r="AD51" s="59">
         <f t="shared" si="12"/>
-        <v>171680000000000.28</v>
+        <v>161500141813518.13</v>
       </c>
       <c r="AE51" s="59">
         <f t="shared" si="12"/>
-        <v>175050000000000.19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.75">
+        <v>164870141813518.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="61" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B54" s="59">
         <v>2021</v>
       </c>
@@ -29548,7 +29548,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
         <v>279</v>
       </c>
@@ -29562,51 +29562,51 @@
       </c>
       <c r="D55" s="66">
         <f>D50/CApULAbIFM!$B$2</f>
-        <v>12813333.333332896</v>
+        <v>9508393.7455575112</v>
       </c>
       <c r="E55" s="66">
         <f>E50/CApULAbIFM!$B$2</f>
-        <v>15306666.666666083</v>
+        <v>9355440.6538729072</v>
       </c>
       <c r="F55" s="66">
         <f>F50/CApULAbIFM!$B$2</f>
-        <v>17799999.999999877</v>
+        <v>9664463.3972990736</v>
       </c>
       <c r="G55" s="66">
         <f>G50/CApULAbIFM!$B$2</f>
-        <v>20293333.333333068</v>
+        <v>10037081.937252348</v>
       </c>
       <c r="H55" s="66">
         <f>H50/CApULAbIFM!$B$2</f>
-        <v>22786666.666666254</v>
+        <v>11067867.803837588</v>
       </c>
       <c r="I55" s="66">
         <f>I50/CApULAbIFM!$B$2</f>
-        <v>25279999.999999441</v>
+        <v>13640572.139302948</v>
       </c>
       <c r="J55" s="66">
         <f>J50/CApULAbIFM!$B$2</f>
-        <v>27773333.333332632</v>
+        <v>17229623.312010668</v>
       </c>
       <c r="K55" s="66">
         <f>K50/CApULAbIFM!$B$2</f>
-        <v>30266666.666666422</v>
+        <v>20402896.233119849</v>
       </c>
       <c r="L55" s="66">
         <f>L50/CApULAbIFM!$B$2</f>
-        <v>32759999.999999609</v>
+        <v>24592515.991470896</v>
       </c>
       <c r="M55" s="66">
         <f>M50/CApULAbIFM!$B$2</f>
-        <v>35253333.333332799</v>
+        <v>28600881.307746448</v>
       </c>
       <c r="N55" s="66">
         <f>N50/CApULAbIFM!$B$2</f>
-        <v>37746666.666665986</v>
+        <v>33311698.649608422</v>
       </c>
       <c r="O55" s="66">
         <f>O50/CApULAbIFM!$B$2</f>
-        <v>40239999.999999784</v>
+        <v>38022515.991470993</v>
       </c>
       <c r="P55" s="66">
         <f>P50/CApULAbIFM!$B$2</f>
@@ -29673,7 +29673,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="59" t="s">
         <v>3</v>
       </c>
@@ -29703,107 +29703,107 @@
       </c>
       <c r="H56" s="59">
         <f>H51/TNC_summary!$C$10</f>
-        <v>24246553.726331349</v>
+        <v>23988937.516587194</v>
       </c>
       <c r="I56" s="59">
         <f>I51/TNC_summary!$C$10</f>
-        <v>28995512.93234513</v>
+        <v>25420598.436868832</v>
       </c>
       <c r="J56" s="59">
         <f>J51/TNC_summary!$C$10</f>
-        <v>33744472.138360754</v>
+        <v>28585055.782905638</v>
       </c>
       <c r="K56" s="59">
         <f>K51/TNC_summary!$C$10</f>
-        <v>38493431.344374537</v>
+        <v>33334014.988919422</v>
       </c>
       <c r="L56" s="59">
         <f>L51/TNC_summary!$C$10</f>
-        <v>43242390.550388314</v>
+        <v>38082974.194933198</v>
       </c>
       <c r="M56" s="59">
         <f>M51/TNC_summary!$C$10</f>
-        <v>47991349.756403945</v>
+        <v>42831933.40094883</v>
       </c>
       <c r="N56" s="59">
         <f>N51/TNC_summary!$C$10</f>
-        <v>52740308.962417729</v>
+        <v>47580892.606962614</v>
       </c>
       <c r="O56" s="59">
         <f>O51/TNC_summary!$C$10</f>
-        <v>57489268.168431513</v>
+        <v>52329851.812976398</v>
       </c>
       <c r="P56" s="59">
         <f>P51/TNC_summary!$C$10</f>
-        <v>62238227.374445289</v>
+        <v>57078811.018990166</v>
       </c>
       <c r="Q56" s="59">
         <f>Q51/TNC_summary!$C$10</f>
-        <v>64032391.258041315</v>
+        <v>58872974.902586199</v>
       </c>
       <c r="R56" s="59">
         <f>R51/TNC_summary!$C$10</f>
-        <v>65826555.141636886</v>
+        <v>60667138.786181763</v>
       </c>
       <c r="S56" s="59">
         <f>S51/TNC_summary!$C$10</f>
-        <v>67620719.025232449</v>
+        <v>62461302.669777334</v>
       </c>
       <c r="T56" s="59">
         <f>T51/TNC_summary!$C$10</f>
-        <v>69414882.908828005</v>
+        <v>64255466.55337289</v>
       </c>
       <c r="U56" s="59">
         <f>U51/TNC_summary!$C$10</f>
-        <v>71209046.792423576</v>
+        <v>66049630.436968461</v>
       </c>
       <c r="V56" s="59">
         <f>V51/TNC_summary!$C$10</f>
-        <v>73003210.676019147</v>
+        <v>67843794.320564032</v>
       </c>
       <c r="W56" s="59">
         <f>W51/TNC_summary!$C$10</f>
-        <v>74797374.559614718</v>
+        <v>69637958.204159588</v>
       </c>
       <c r="X56" s="59">
         <f>X51/TNC_summary!$C$10</f>
-        <v>76591538.443210274</v>
+        <v>71432122.087755159</v>
       </c>
       <c r="Y56" s="59">
         <f>Y51/TNC_summary!$C$10</f>
-        <v>78385702.32680583</v>
+        <v>73226285.971350715</v>
       </c>
       <c r="Z56" s="59">
         <f>Z51/TNC_summary!$C$10</f>
-        <v>80179866.210401401</v>
+        <v>75020449.854946285</v>
       </c>
       <c r="AA56" s="59">
         <f>AA51/TNC_summary!$C$10</f>
-        <v>81887869.681508347</v>
+        <v>76728453.326053217</v>
       </c>
       <c r="AB56" s="59">
         <f>AB51/TNC_summary!$C$10</f>
-        <v>83595873.152614802</v>
+        <v>78436456.797159687</v>
       </c>
       <c r="AC56" s="59">
         <f>AC51/TNC_summary!$C$10</f>
-        <v>85303876.623721287</v>
+        <v>80144460.268266171</v>
       </c>
       <c r="AD56" s="59">
         <f>AD51/TNC_summary!$C$10</f>
-        <v>87011880.094827756</v>
+        <v>81852463.739372641</v>
       </c>
       <c r="AE56" s="59">
         <f>AE51/TNC_summary!$C$10</f>
-        <v>88719883.565934241</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.75">
+        <v>83560467.210479125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" s="61" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B59" s="59">
         <v>2021</v>
       </c>
@@ -29895,7 +29895,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A60" s="59" t="s">
         <v>279</v>
       </c>
@@ -29909,51 +29909,51 @@
       </c>
       <c r="D60" s="66">
         <f t="shared" si="13"/>
-        <v>12813333.333332896</v>
+        <v>9508393.7455575112</v>
       </c>
       <c r="E60" s="66">
         <f t="shared" si="13"/>
-        <v>15306666.666666083</v>
+        <v>9355440.6538729072</v>
       </c>
       <c r="F60" s="66">
         <f t="shared" si="13"/>
-        <v>17799999.999999877</v>
+        <v>9664463.3972990736</v>
       </c>
       <c r="G60" s="66">
         <f t="shared" si="13"/>
-        <v>20293333.333333068</v>
+        <v>10037081.937252348</v>
       </c>
       <c r="H60" s="66">
         <f t="shared" si="13"/>
-        <v>22786666.666666254</v>
+        <v>11067867.803837588</v>
       </c>
       <c r="I60" s="66">
         <f>I55</f>
-        <v>25279999.999999441</v>
+        <v>13640572.139302948</v>
       </c>
       <c r="J60" s="66">
         <f t="shared" si="13"/>
-        <v>27773333.333332632</v>
+        <v>17229623.312010668</v>
       </c>
       <c r="K60" s="66">
         <f t="shared" si="13"/>
-        <v>30266666.666666422</v>
+        <v>20402896.233119849</v>
       </c>
       <c r="L60" s="66">
         <f t="shared" si="13"/>
-        <v>32759999.999999609</v>
+        <v>24592515.991470896</v>
       </c>
       <c r="M60" s="66">
         <f t="shared" si="13"/>
-        <v>35253333.333332799</v>
+        <v>28600881.307746448</v>
       </c>
       <c r="N60" s="66">
         <f t="shared" si="13"/>
-        <v>37746666.666665986</v>
+        <v>33311698.649608422</v>
       </c>
       <c r="O60" s="66">
         <f t="shared" si="13"/>
-        <v>40239999.999999784</v>
+        <v>38022515.991470993</v>
       </c>
       <c r="P60" s="66">
         <f t="shared" si="13"/>
@@ -30020,7 +30020,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" s="59" t="s">
         <v>3</v>
       </c>
@@ -30050,15 +30050,15 @@
       </c>
       <c r="H61" s="59">
         <f t="shared" si="14"/>
-        <v>4748959.2060137838</v>
+        <v>4491342.9962696284</v>
       </c>
       <c r="I61" s="59">
         <f t="shared" si="14"/>
-        <v>4748959.2060137801</v>
+        <v>1431660.9202816375</v>
       </c>
       <c r="J61" s="59">
         <f t="shared" si="14"/>
-        <v>4748959.2060156241</v>
+        <v>3164457.3460368067</v>
       </c>
       <c r="K61" s="59">
         <f t="shared" si="14"/>
@@ -30082,19 +30082,19 @@
       </c>
       <c r="P61" s="59">
         <f t="shared" si="14"/>
-        <v>4748959.2060137764</v>
+        <v>4748959.2060137689</v>
       </c>
       <c r="Q61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835960254</v>
+        <v>1794163.8835960329</v>
       </c>
       <c r="R61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955709</v>
+        <v>1794163.8835955635</v>
       </c>
       <c r="S61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955635</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="T61" s="59">
         <f t="shared" si="14"/>
@@ -30110,11 +30110,11 @@
       </c>
       <c r="W61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.8835955709</v>
+        <v>1794163.883595556</v>
       </c>
       <c r="X61" s="59">
         <f t="shared" si="14"/>
-        <v>1794163.883595556</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="Y61" s="59">
         <f t="shared" si="14"/>
@@ -30126,11 +30126,11 @@
       </c>
       <c r="AA61" s="59">
         <f t="shared" si="14"/>
-        <v>1708003.4711069465</v>
+        <v>1708003.4711069316</v>
       </c>
       <c r="AB61" s="59">
         <f t="shared" si="14"/>
-        <v>1708003.4711064547</v>
+        <v>1708003.4711064696</v>
       </c>
       <c r="AC61" s="59">
         <f t="shared" si="14"/>
@@ -30153,17 +30153,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171879A6-D0D6-49AA-B160-18EBF002316C}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1328125" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>335</v>
       </c>
@@ -30172,7 +30172,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>336</v>
       </c>
@@ -30180,7 +30180,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>338</v>
       </c>
@@ -30193,72 +30193,72 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0FF694-673B-4399-A04F-DA1E9EEB856B}">
   <dimension ref="A1:EC52"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="16" x14ac:dyDescent="0.8"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.54296875" style="10"/>
-    <col min="3" max="3" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" style="16" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.86328125" style="16" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="15.86328125" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.86328125" style="16" hidden="1" customWidth="1"/>
+    <col min="1" max="2" width="11.5703125" style="10"/>
+    <col min="3" max="3" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="16" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="16" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" style="16" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" style="16" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="13.54296875" style="16" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="16.1328125" style="37" customWidth="1"/>
-    <col min="15" max="15" width="13.54296875" style="10" hidden="1" customWidth="1"/>
-    <col min="16" max="18" width="13.54296875" style="10" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="16" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="16" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" style="37" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="10" hidden="1" customWidth="1"/>
+    <col min="16" max="18" width="13.5703125" style="10" customWidth="1"/>
     <col min="19" max="19" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="20" max="21" width="11.7265625" style="10" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="15.26953125" style="16" customWidth="1"/>
-    <col min="23" max="23" width="11.7265625" style="10" hidden="1" customWidth="1"/>
+    <col min="20" max="21" width="11.7109375" style="10" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="15.28515625" style="16" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" style="10" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="11.7265625" style="10" hidden="1" customWidth="1"/>
+    <col min="25" max="26" width="11.7109375" style="10" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="16" style="16" customWidth="1"/>
-    <col min="28" max="28" width="11.7265625" style="10" hidden="1" customWidth="1"/>
-    <col min="29" max="31" width="11.7265625" style="10" customWidth="1"/>
-    <col min="32" max="41" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="11.7265625" style="10" customWidth="1"/>
-    <col min="44" max="44" width="13.86328125" style="38" customWidth="1"/>
-    <col min="45" max="51" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="10" hidden="1" customWidth="1"/>
+    <col min="29" max="31" width="11.7109375" style="10" customWidth="1"/>
+    <col min="32" max="41" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="11.7109375" style="10" customWidth="1"/>
+    <col min="44" max="44" width="13.85546875" style="38" customWidth="1"/>
+    <col min="45" max="51" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="55" max="57" width="11.7265625" style="10" customWidth="1"/>
-    <col min="58" max="67" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.54296875" style="10"/>
+    <col min="55" max="57" width="11.7109375" style="10" customWidth="1"/>
+    <col min="58" max="67" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.5703125" style="10"/>
     <col min="69" max="72" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="11.54296875" style="10"/>
+    <col min="73" max="73" width="11.5703125" style="10"/>
     <col min="74" max="77" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="11.54296875" style="10"/>
-    <col min="79" max="82" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="11.54296875" style="10"/>
-    <col min="84" max="87" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.5703125" style="10"/>
+    <col min="79" max="82" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="11.5703125" style="10"/>
+    <col min="84" max="87" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="89" max="90" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="15.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="15.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="92" max="92" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="94" max="95" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="98" max="100" width="11.7265625" style="10" customWidth="1"/>
-    <col min="101" max="101" width="11.54296875" style="10"/>
-    <col min="102" max="103" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="11.54296875" style="10"/>
-    <col min="107" max="108" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="111" max="113" width="11.7265625" style="10" customWidth="1"/>
-    <col min="114" max="114" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="115" max="123" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="11.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="125" max="133" width="11.86328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="134" max="16384" width="11.54296875" style="10"/>
+    <col min="93" max="93" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="94" max="95" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="98" max="100" width="11.7109375" style="10" customWidth="1"/>
+    <col min="101" max="101" width="11.5703125" style="10"/>
+    <col min="102" max="103" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="11.5703125" style="10"/>
+    <col min="107" max="108" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="111" max="113" width="11.7109375" style="10" customWidth="1"/>
+    <col min="114" max="114" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="115" max="123" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="125" max="133" width="11.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="134" max="16384" width="11.5703125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:133" x14ac:dyDescent="0.25">
       <c r="F1" s="10"/>
       <c r="G1" s="10" t="s">
         <v>59</v>
@@ -30351,7 +30351,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:133" x14ac:dyDescent="0.25">
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
@@ -30396,7 +30396,7 @@
       <c r="DH2" s="15"/>
       <c r="DI2" s="15"/>
     </row>
-    <row r="3" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>71</v>
       </c>
@@ -30797,7 +30797,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
@@ -31177,7 +31177,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="5" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="5" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
@@ -31557,7 +31557,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="6" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="6" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
@@ -31937,7 +31937,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="7" spans="1:133" s="16" customFormat="1" x14ac:dyDescent="0.8">
+    <row r="7" spans="1:133" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
@@ -32344,7 +32344,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="8" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="8" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>18</v>
       </c>
@@ -32745,7 +32745,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="9" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
@@ -33146,7 +33146,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="10" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
@@ -33547,7 +33547,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="11" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="11" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -33927,7 +33927,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="12" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="12" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>17</v>
       </c>
@@ -34307,7 +34307,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="13" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
@@ -34687,7 +34687,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="14" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="14" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>19</v>
       </c>
@@ -35067,7 +35067,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="15" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="15" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>21</v>
       </c>
@@ -35447,7 +35447,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="16" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="16" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>16</v>
       </c>
@@ -35827,7 +35827,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="17" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
@@ -36207,7 +36207,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="18" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="18" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>20</v>
       </c>
@@ -36587,7 +36587,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="19" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="19" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -36967,7 +36967,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="20" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="20" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>29</v>
       </c>
@@ -37347,7 +37347,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="21" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="21" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>26</v>
       </c>
@@ -37748,7 +37748,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="22" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="22" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
@@ -38149,7 +38149,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="23" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="23" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>32</v>
       </c>
@@ -38529,7 +38529,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="24" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>34</v>
       </c>
@@ -38930,7 +38930,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="25" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="25" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>24</v>
       </c>
@@ -39310,7 +39310,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="26" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="26" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>37</v>
       </c>
@@ -39690,7 +39690,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="27" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="27" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
@@ -40070,7 +40070,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="28" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="28" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>36</v>
       </c>
@@ -40450,7 +40450,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="29" spans="1:133" s="12" customFormat="1" x14ac:dyDescent="0.8">
+    <row r="29" spans="1:133" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
         <v>39</v>
       </c>
@@ -40841,7 +40841,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="30" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="30" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>40</v>
       </c>
@@ -41221,7 +41221,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="31" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="31" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>43</v>
       </c>
@@ -41622,7 +41622,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="32" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="32" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>42</v>
       </c>
@@ -42002,7 +42002,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="33" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="33" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>46</v>
       </c>
@@ -42403,7 +42403,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="34" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="34" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>27</v>
       </c>
@@ -42804,7 +42804,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="35" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="35" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>33</v>
       </c>
@@ -43184,7 +43184,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="36" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="36" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>48</v>
       </c>
@@ -43564,7 +43564,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="37" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="37" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>30</v>
       </c>
@@ -43944,7 +43944,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="38" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="38" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>45</v>
       </c>
@@ -44345,7 +44345,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="39" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="39" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>50</v>
       </c>
@@ -44725,7 +44725,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="40" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="40" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>52</v>
       </c>
@@ -45126,7 +45126,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="41" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="41" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>35</v>
       </c>
@@ -45506,7 +45506,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="42" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="42" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>47</v>
       </c>
@@ -45886,7 +45886,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="43" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="43" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>38</v>
       </c>
@@ -46266,7 +46266,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="44" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="44" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>41</v>
       </c>
@@ -46646,7 +46646,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="45" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="45" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>49</v>
       </c>
@@ -47026,7 +47026,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="46" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="46" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>54</v>
       </c>
@@ -47427,7 +47427,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="47" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="47" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>44</v>
       </c>
@@ -47828,7 +47828,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="48" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="48" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>51</v>
       </c>
@@ -48229,7 +48229,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="49" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="49" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>56</v>
       </c>
@@ -48609,7 +48609,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="50" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="50" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>55</v>
       </c>
@@ -48989,7 +48989,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="51" spans="1:133" x14ac:dyDescent="0.8">
+    <row r="51" spans="1:133" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>53</v>
       </c>
@@ -49369,7 +49369,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="52" spans="1:133" s="30" customFormat="1" x14ac:dyDescent="0.8">
+    <row r="52" spans="1:133" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
         <v>239</v>
       </c>
@@ -49568,13 +49568,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59812A91-DF51-48C6-9139-7A65100E3E7B}">
   <dimension ref="A2:V22"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.1328125" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B2" s="39" t="s">
         <v>244</v>
       </c>
@@ -49599,7 +49599,7 @@
       <c r="U2" s="40"/>
       <c r="V2" s="40"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>245</v>
       </c>
@@ -49624,12 +49624,12 @@
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>247</v>
       </c>
@@ -49637,7 +49637,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>249</v>
       </c>
@@ -49649,7 +49649,7 @@
         <v>252444615.67210001</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -49661,7 +49661,7 @@
         <v>127945483.62911001</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>253</v>
       </c>
@@ -49670,7 +49670,7 @@
         <v>3554041.2119197226</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>332</v>
       </c>
@@ -49679,7 +49679,7 @@
         <v>1973063.9059045622</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>247</v>
       </c>
@@ -49687,7 +49687,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>249</v>
       </c>
@@ -49699,7 +49699,7 @@
         <v>37999999.998844996</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -49711,7 +49711,7 @@
         <v>6764601.5311640995</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>253</v>
       </c>
@@ -49720,7 +49720,7 @@
         <v>187905.59808789165</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>332</v>
       </c>
@@ -49729,11 +49729,11 @@
         <v>5617477.9584253943</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
       <c r="C17" s="6"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>247</v>
       </c>
@@ -49741,7 +49741,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>249</v>
       </c>
@@ -49753,7 +49753,7 @@
         <v>116013193.64404109</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -49765,7 +49765,7 @@
         <v>6813914.8343433412</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>253</v>
       </c>
@@ -49774,7 +49774,7 @@
         <v>189275.41206509282</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>332</v>
       </c>
@@ -49791,17 +49791,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3877CA7D-439B-4474-847A-349C8907D325}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.40625" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>256</v>
       </c>
@@ -49809,7 +49809,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>255</v>
       </c>
@@ -49818,7 +49818,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>258</v>
       </c>
@@ -49826,7 +49826,7 @@
         <v>890909</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
         <v>259</v>
       </c>
@@ -49835,7 +49835,7 @@
         <v>3390909</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
         <v>260</v>
       </c>
@@ -49855,15 +49855,15 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:BL66"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.86328125" customWidth="1"/>
+    <col min="1" max="1" width="73.85546875" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="36.1328125" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>269</v>
       </c>
@@ -49931,17 +49931,17 @@
       <c r="BK1" s="47"/>
       <c r="BL1" s="47"/>
     </row>
-    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:64" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>270</v>
       </c>
       <c r="B2" s="49"/>
     </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
     </row>
-    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45" t="s">
         <v>271</v>
       </c>
@@ -50009,7 +50009,7 @@
       <c r="BK4" s="47"/>
       <c r="BL4" s="47"/>
     </row>
-    <row r="5" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
         <v>272</v>
       </c>
@@ -50017,15 +50017,15 @@
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A6" s="50"/>
     </row>
-    <row r="7" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
         <v>274</v>
       </c>
@@ -50037,7 +50037,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>276</v>
       </c>
@@ -50049,7 +50049,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A10" s="53" t="s">
         <v>277</v>
       </c>
@@ -50061,7 +50061,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
         <v>278</v>
       </c>
@@ -50073,7 +50073,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="12" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>280</v>
       </c>
@@ -50085,7 +50085,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A13" s="53" t="s">
         <v>280</v>
       </c>
@@ -50097,7 +50097,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>280</v>
       </c>
@@ -50109,7 +50109,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
         <v>280</v>
       </c>
@@ -50121,7 +50121,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>281</v>
       </c>
@@ -50133,7 +50133,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>280</v>
       </c>
@@ -50145,7 +50145,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="18" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>282</v>
       </c>
@@ -50157,7 +50157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>283</v>
       </c>
@@ -50169,13 +50169,13 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A21" s="52" t="s">
         <v>351</v>
       </c>
       <c r="B21" s="51"/>
     </row>
-    <row r="22" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
         <v>279</v>
       </c>
@@ -50184,7 +50184,7 @@
         <v>102049999.99999999</v>
       </c>
     </row>
-    <row r="23" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>3</v>
       </c>
@@ -50193,15 +50193,15 @@
         <v>117750000</v>
       </c>
     </row>
-    <row r="25" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="26" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A27" s="50"/>
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
@@ -50267,7 +50267,7 @@
       <c r="BK27" s="49"/>
       <c r="BL27" s="49"/>
     </row>
-    <row r="28" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -50333,7 +50333,7 @@
       <c r="BK28" s="49"/>
       <c r="BL28" s="49"/>
     </row>
-    <row r="29" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A29" s="49"/>
       <c r="B29" s="49"/>
       <c r="C29" s="49"/>
@@ -50399,7 +50399,7 @@
       <c r="BK29" s="55"/>
       <c r="BL29" s="55"/>
     </row>
-    <row r="30" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
@@ -50465,7 +50465,7 @@
       <c r="BK30" s="49"/>
       <c r="BL30" s="49"/>
     </row>
-    <row r="31" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A31" s="49"/>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -50531,7 +50531,7 @@
       <c r="BK31" s="49"/>
       <c r="BL31" s="49"/>
     </row>
-    <row r="32" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -50597,7 +50597,7 @@
       <c r="BK32" s="49"/>
       <c r="BL32" s="49"/>
     </row>
-    <row r="33" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
       <c r="B33" s="49"/>
       <c r="C33" s="49"/>
@@ -50663,7 +50663,7 @@
       <c r="BK33" s="49"/>
       <c r="BL33" s="49"/>
     </row>
-    <row r="34" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
       <c r="B34" s="49"/>
       <c r="C34" s="49"/>
@@ -50729,7 +50729,7 @@
       <c r="BK34" s="49"/>
       <c r="BL34" s="49"/>
     </row>
-    <row r="35" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -50795,7 +50795,7 @@
       <c r="BK35" s="49"/>
       <c r="BL35" s="49"/>
     </row>
-    <row r="36" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="49"/>
       <c r="C36" s="49"/>
@@ -50861,7 +50861,7 @@
       <c r="BK36" s="49"/>
       <c r="BL36" s="49"/>
     </row>
-    <row r="37" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A37" s="49"/>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
@@ -50927,20 +50927,20 @@
       <c r="BK37" s="49"/>
       <c r="BL37" s="49"/>
     </row>
-    <row r="39" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="55"/>
     </row>
-    <row r="40" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="55"/>
       <c r="D40" s="54"/>
     </row>
-    <row r="42" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="56"/>
     </row>
-    <row r="43" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
       <c r="B43" s="49"/>
       <c r="C43" s="49"/>
@@ -51006,7 +51006,7 @@
       <c r="BK43" s="49"/>
       <c r="BL43" s="49"/>
     </row>
-    <row r="44" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
@@ -51072,7 +51072,7 @@
       <c r="BK44" s="49"/>
       <c r="BL44" s="49"/>
     </row>
-    <row r="45" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A45" s="49"/>
       <c r="B45" s="49"/>
       <c r="C45" s="49"/>
@@ -51138,7 +51138,7 @@
       <c r="BK45" s="49"/>
       <c r="BL45" s="49"/>
     </row>
-    <row r="46" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A46" s="49"/>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>
@@ -51204,7 +51204,7 @@
       <c r="BK46" s="55"/>
       <c r="BL46" s="55"/>
     </row>
-    <row r="47" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A47" s="49"/>
       <c r="B47" s="49"/>
       <c r="C47" s="49"/>
@@ -51270,7 +51270,7 @@
       <c r="BK47" s="49"/>
       <c r="BL47" s="49"/>
     </row>
-    <row r="48" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A48" s="49"/>
       <c r="B48" s="49"/>
       <c r="C48" s="49"/>
@@ -51336,7 +51336,7 @@
       <c r="BK48" s="49"/>
       <c r="BL48" s="49"/>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A49" s="49"/>
       <c r="B49" s="49"/>
       <c r="C49" s="49"/>
@@ -51402,7 +51402,7 @@
       <c r="BK49" s="49"/>
       <c r="BL49" s="49"/>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A50" s="49"/>
       <c r="B50" s="49"/>
       <c r="C50" s="49"/>
@@ -51468,7 +51468,7 @@
       <c r="BK50" s="49"/>
       <c r="BL50" s="49"/>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A51" s="49"/>
       <c r="B51" s="49"/>
       <c r="C51" s="49"/>
@@ -51534,7 +51534,7 @@
       <c r="BK51" s="49"/>
       <c r="BL51" s="49"/>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A52" s="49"/>
       <c r="B52" s="49"/>
       <c r="C52" s="49"/>
@@ -51600,7 +51600,7 @@
       <c r="BK52" s="49"/>
       <c r="BL52" s="49"/>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A53" s="49"/>
       <c r="B53" s="49"/>
       <c r="C53" s="49"/>
@@ -51666,7 +51666,7 @@
       <c r="BK53" s="49"/>
       <c r="BL53" s="49"/>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A54" s="49"/>
       <c r="B54" s="49"/>
       <c r="C54" s="49"/>
@@ -51732,25 +51732,25 @@
       <c r="BK54" s="49"/>
       <c r="BL54" s="49"/>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A56" s="49"/>
       <c r="B56" s="55"/>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A57" s="49"/>
       <c r="B57" s="55"/>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A59" s="49"/>
       <c r="B59" s="57"/>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A61" s="50"/>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A62" s="50"/>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
@@ -51780,7 +51780,7 @@
       <c r="AE63" s="6"/>
       <c r="AF63" s="6"/>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
       <c r="D64" s="55"/>
       <c r="E64" s="55"/>
       <c r="F64" s="55"/>
@@ -51811,7 +51811,7 @@
       <c r="AE64" s="55"/>
       <c r="AF64" s="55"/>
     </row>
-    <row r="65" spans="4:32" x14ac:dyDescent="0.75">
+    <row r="65" spans="4:32" x14ac:dyDescent="0.25">
       <c r="D65" s="55"/>
       <c r="E65" s="55"/>
       <c r="F65" s="55"/>
@@ -51842,7 +51842,7 @@
       <c r="AE65" s="55"/>
       <c r="AF65" s="55"/>
     </row>
-    <row r="66" spans="4:32" x14ac:dyDescent="0.75">
+    <row r="66" spans="4:32" x14ac:dyDescent="0.25">
       <c r="D66" s="55"/>
       <c r="E66" s="55"/>
       <c r="F66" s="55"/>
@@ -51885,13 +51885,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.26953125" customWidth="1"/>
-    <col min="2" max="31" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="31" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -51986,7 +51986,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -52081,7 +52081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -52111,15 +52111,15 @@
       </c>
       <c r="H3" s="3">
         <f>'EPA land and ag calcs'!H61</f>
-        <v>4748959.2060137838</v>
+        <v>4491342.9962696284</v>
       </c>
       <c r="I3" s="3">
         <f>'EPA land and ag calcs'!I61</f>
-        <v>4748959.2060137801</v>
+        <v>1431660.9202816375</v>
       </c>
       <c r="J3" s="3">
         <f>'EPA land and ag calcs'!J61</f>
-        <v>4748959.2060156241</v>
+        <v>3164457.3460368067</v>
       </c>
       <c r="K3" s="3">
         <f>'EPA land and ag calcs'!K61</f>
@@ -52143,19 +52143,19 @@
       </c>
       <c r="P3" s="3">
         <f>'EPA land and ag calcs'!P61</f>
-        <v>4748959.2060137764</v>
+        <v>4748959.2060137689</v>
       </c>
       <c r="Q3" s="3">
         <f>'EPA land and ag calcs'!Q61</f>
-        <v>1794163.8835960254</v>
+        <v>1794163.8835960329</v>
       </c>
       <c r="R3" s="3">
         <f>'EPA land and ag calcs'!R61</f>
-        <v>1794163.8835955709</v>
+        <v>1794163.8835955635</v>
       </c>
       <c r="S3" s="3">
         <f>'EPA land and ag calcs'!S61</f>
-        <v>1794163.8835955635</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="T3" s="3">
         <f>'EPA land and ag calcs'!T61</f>
@@ -52171,11 +52171,11 @@
       </c>
       <c r="W3" s="3">
         <f>'EPA land and ag calcs'!W61</f>
-        <v>1794163.8835955709</v>
+        <v>1794163.883595556</v>
       </c>
       <c r="X3" s="3">
         <f>'EPA land and ag calcs'!X61</f>
-        <v>1794163.883595556</v>
+        <v>1794163.8835955709</v>
       </c>
       <c r="Y3" s="3">
         <f>'EPA land and ag calcs'!Y61</f>
@@ -52187,11 +52187,11 @@
       </c>
       <c r="AA3" s="3">
         <f>'EPA land and ag calcs'!AA61</f>
-        <v>1708003.4711069465</v>
+        <v>1708003.4711069316</v>
       </c>
       <c r="AB3" s="3">
         <f>'EPA land and ag calcs'!AB61</f>
-        <v>1708003.4711064547</v>
+        <v>1708003.4711064696</v>
       </c>
       <c r="AC3" s="3">
         <f>'EPA land and ag calcs'!AC61</f>
@@ -52206,7 +52206,7 @@
         <v>1708003.4711064845</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -52220,51 +52220,51 @@
       </c>
       <c r="D4" s="3">
         <f>'EPA land and ag calcs'!D60</f>
-        <v>12813333.333332896</v>
+        <v>9508393.7455575112</v>
       </c>
       <c r="E4" s="3">
         <f>'EPA land and ag calcs'!E60</f>
-        <v>15306666.666666083</v>
+        <v>9355440.6538729072</v>
       </c>
       <c r="F4" s="3">
         <f>'EPA land and ag calcs'!F60</f>
-        <v>17799999.999999877</v>
+        <v>9664463.3972990736</v>
       </c>
       <c r="G4" s="3">
         <f>'EPA land and ag calcs'!G60</f>
-        <v>20293333.333333068</v>
+        <v>10037081.937252348</v>
       </c>
       <c r="H4" s="3">
         <f>'EPA land and ag calcs'!H60</f>
-        <v>22786666.666666254</v>
+        <v>11067867.803837588</v>
       </c>
       <c r="I4" s="3">
         <f>'EPA land and ag calcs'!I60</f>
-        <v>25279999.999999441</v>
+        <v>13640572.139302948</v>
       </c>
       <c r="J4" s="3">
         <f>'EPA land and ag calcs'!J60</f>
-        <v>27773333.333332632</v>
+        <v>17229623.312010668</v>
       </c>
       <c r="K4" s="3">
         <f>'EPA land and ag calcs'!K60</f>
-        <v>30266666.666666422</v>
+        <v>20402896.233119849</v>
       </c>
       <c r="L4" s="3">
         <f>'EPA land and ag calcs'!L60</f>
-        <v>32759999.999999609</v>
+        <v>24592515.991470896</v>
       </c>
       <c r="M4" s="3">
         <f>'EPA land and ag calcs'!M60</f>
-        <v>35253333.333332799</v>
+        <v>28600881.307746448</v>
       </c>
       <c r="N4" s="3">
         <f>'EPA land and ag calcs'!N60</f>
-        <v>37746666.666665986</v>
+        <v>33311698.649608422</v>
       </c>
       <c r="O4" s="3">
         <f>'EPA land and ag calcs'!O60</f>
-        <v>40239999.999999784</v>
+        <v>38022515.991470993</v>
       </c>
       <c r="P4" s="3">
         <f>'EPA land and ag calcs'!P60</f>
@@ -52331,7 +52331,7 @@
         <v>54899999.99999994</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -52426,7 +52426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>6</v>
       </c>
@@ -52550,7 +52550,7 @@
         <v>116927.89655172414</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>7</v>
       </c>
